--- a/261009_課題リスト.xlsx
+++ b/261009_課題リスト.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="325" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="325" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="課題リスト" sheetId="1" state="visible" r:id="rId1"/>
@@ -254,7 +254,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -336,9 +336,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -381,9 +378,6 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -396,18 +390,12 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -423,18 +411,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -444,42 +420,55 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -487,6 +476,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -496,9 +488,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -509,6 +510,9 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="31" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -524,98 +528,44 @@
     <xf numFmtId="166" fontId="2" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -964,22 +914,22 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="45" customHeight="1"/>
   <cols>
     <col width="7.88671875" customWidth="1" style="15" min="1" max="1"/>
-    <col width="4.88671875" customWidth="1" style="28" min="2" max="7"/>
-    <col width="10.88671875" customWidth="1" style="84" min="8" max="8"/>
+    <col width="4.88671875" customWidth="1" style="27" min="2" max="7"/>
+    <col width="12.77734375" bestFit="1" customWidth="1" style="85" min="8" max="8"/>
     <col width="10.88671875" customWidth="1" style="15" min="9" max="9"/>
-    <col width="50.88671875" customWidth="1" style="82" min="10" max="10"/>
+    <col width="50.88671875" customWidth="1" style="78" min="10" max="10"/>
     <col width="10.88671875" customWidth="1" style="15" min="11" max="11"/>
-    <col width="70.6640625" customWidth="1" style="82" min="12" max="12"/>
-    <col width="14.6640625" customWidth="1" style="85" min="13" max="13"/>
+    <col width="70.6640625" customWidth="1" style="78" min="12" max="12"/>
+    <col width="14.6640625" customWidth="1" style="86" min="13" max="13"/>
     <col width="12.33203125" customWidth="1" style="15" min="14" max="14"/>
-    <col width="14" bestFit="1" customWidth="1" style="31" min="15" max="15"/>
-    <col width="7.88671875" customWidth="1" style="82" min="16" max="16"/>
+    <col width="14" bestFit="1" customWidth="1" style="30" min="15" max="15"/>
+    <col width="7.88671875" customWidth="1" style="78" min="16" max="16"/>
     <col width="36.109375" customWidth="1" style="10" min="17" max="17"/>
-    <col width="9" customWidth="1" style="10" min="18" max="18"/>
-    <col width="9" customWidth="1" style="10" min="19" max="16384"/>
+    <col width="9" customWidth="1" style="10" min="18" max="19"/>
+    <col width="9" customWidth="1" style="10" min="20" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" s="86">
+    <row r="1" ht="21.75" customHeight="1" s="87">
       <c r="A1" s="7" t="inlineStr">
         <is>
           <t>椙山女学園　星が丘キャンパス大学会館食堂リニューアル工事　課題リスト</t>
@@ -996,11 +946,11 @@
       <c r="J1" s="8" t="n"/>
       <c r="K1" s="8" t="n"/>
       <c r="L1" s="9" t="n"/>
-      <c r="M1" s="87" t="n"/>
+      <c r="M1" s="88" t="n"/>
       <c r="N1" s="8" t="n"/>
-      <c r="O1" s="81" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="86">
+      <c r="O1" s="89" t="n"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="87">
       <c r="A2" s="11" t="n"/>
       <c r="B2" s="12" t="n"/>
       <c r="C2" s="12" t="n"/>
@@ -1013,915 +963,915 @@
       <c r="J2" s="12" t="n"/>
       <c r="K2" s="13" t="n"/>
       <c r="L2" s="14" t="n"/>
-      <c r="M2" s="88" t="n"/>
+      <c r="M2" s="90" t="n"/>
       <c r="N2" s="8" t="n"/>
       <c r="O2" s="15" t="n"/>
-      <c r="P2" s="64" t="inlineStr">
+      <c r="P2" s="55" t="inlineStr">
         <is>
           <t>［凡例］　椙山女学園：SJ、日建設計：NS、清水建設：SC、東山遊園：HY、竹中工務店：TK、丸善雄松堂：MY</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25.2" customHeight="1" s="86">
-      <c r="A3" s="77" t="inlineStr">
+    <row r="3" ht="25.2" customHeight="1" s="87">
+      <c r="A3" s="72" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B3" s="74" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>対象区分</t>
         </is>
       </c>
-      <c r="C3" s="75" t="n"/>
-      <c r="D3" s="75" t="n"/>
-      <c r="E3" s="75" t="n"/>
-      <c r="F3" s="75" t="n"/>
-      <c r="G3" s="76" t="n"/>
-      <c r="H3" s="89" t="inlineStr">
+      <c r="C3" s="82" t="n"/>
+      <c r="D3" s="82" t="n"/>
+      <c r="E3" s="82" t="n"/>
+      <c r="F3" s="82" t="n"/>
+      <c r="G3" s="83" t="n"/>
+      <c r="H3" s="91" t="inlineStr">
         <is>
           <t>発信日</t>
         </is>
       </c>
-      <c r="I3" s="77" t="inlineStr">
+      <c r="I3" s="72" t="inlineStr">
         <is>
           <t>発信者</t>
         </is>
       </c>
-      <c r="J3" s="77" t="inlineStr">
+      <c r="J3" s="72" t="inlineStr">
         <is>
           <t>懸案事項の概要</t>
         </is>
       </c>
-      <c r="K3" s="77" t="inlineStr">
+      <c r="K3" s="72" t="inlineStr">
         <is>
           <t>検討対象</t>
         </is>
       </c>
-      <c r="L3" s="77" t="inlineStr">
+      <c r="L3" s="72" t="inlineStr">
         <is>
           <t>回答／経過／対策／決定事項</t>
         </is>
       </c>
-      <c r="M3" s="90" t="inlineStr">
+      <c r="M3" s="92" t="inlineStr">
         <is>
           <t>概算金額(税抜)</t>
         </is>
       </c>
-      <c r="N3" s="79" t="inlineStr">
+      <c r="N3" s="74" t="inlineStr">
         <is>
           <t>期限日</t>
         </is>
       </c>
-      <c r="O3" s="79" t="inlineStr">
+      <c r="O3" s="74" t="inlineStr">
         <is>
           <t>完了日</t>
         </is>
       </c>
-      <c r="P3" s="79" t="inlineStr">
+      <c r="P3" s="74" t="inlineStr">
         <is>
           <t>指示書
 番号</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="25.2" customHeight="1" s="86" thickBot="1">
-      <c r="A4" s="78" t="n"/>
-      <c r="B4" s="79" t="inlineStr">
+    <row r="4" ht="25.2" customHeight="1" s="87" thickBot="1">
+      <c r="A4" s="84" t="n"/>
+      <c r="B4" s="74" t="inlineStr">
         <is>
           <t>意匠</t>
         </is>
       </c>
-      <c r="C4" s="79" t="inlineStr">
+      <c r="C4" s="74" t="inlineStr">
         <is>
           <t>構造</t>
         </is>
       </c>
-      <c r="D4" s="79" t="inlineStr">
+      <c r="D4" s="74" t="inlineStr">
         <is>
           <t>電気</t>
         </is>
       </c>
-      <c r="E4" s="79" t="inlineStr">
+      <c r="E4" s="74" t="inlineStr">
         <is>
           <t>空調</t>
         </is>
       </c>
-      <c r="F4" s="79" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>衛生</t>
         </is>
       </c>
-      <c r="G4" s="79" t="n"/>
-      <c r="H4" s="78" t="n"/>
-      <c r="I4" s="78" t="n"/>
-      <c r="J4" s="78" t="n"/>
-      <c r="K4" s="78" t="n"/>
-      <c r="L4" s="78" t="n"/>
-      <c r="M4" s="78" t="n"/>
-      <c r="N4" s="78" t="n"/>
-      <c r="O4" s="78" t="n"/>
-      <c r="P4" s="78" t="n"/>
-    </row>
-    <row r="5" ht="60" customFormat="1" customHeight="1" s="82" thickTop="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="G4" s="74" t="n"/>
+      <c r="H4" s="84" t="n"/>
+      <c r="I4" s="84" t="n"/>
+      <c r="J4" s="84" t="n"/>
+      <c r="K4" s="84" t="n"/>
+      <c r="L4" s="84" t="n"/>
+      <c r="M4" s="84" t="n"/>
+      <c r="N4" s="84" t="n"/>
+      <c r="O4" s="84" t="n"/>
+      <c r="P4" s="84" t="n"/>
+    </row>
+    <row r="5" ht="60" customFormat="1" customHeight="1" s="78" thickTop="1">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>例</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>　</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="34" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="34" t="inlineStr">
         <is>
           <t>　</t>
         </is>
       </c>
-      <c r="H5" s="91" t="n">
+      <c r="H5" s="93" t="n">
         <v>45082</v>
       </c>
-      <c r="I5" s="37" t="inlineStr">
+      <c r="I5" s="36" t="inlineStr">
         <is>
           <t>SC□□</t>
         </is>
       </c>
-      <c r="J5" s="38" t="inlineStr">
+      <c r="J5" s="37" t="inlineStr">
         <is>
           <t>2階通路の一部で設計天井高さ内に空調機が納まらない</t>
         </is>
       </c>
-      <c r="K5" s="37" t="inlineStr">
+      <c r="K5" s="36" t="inlineStr">
         <is>
           <t>NS〇〇
 SC△△</t>
         </is>
       </c>
-      <c r="L5" s="39" t="inlineStr">
+      <c r="L5" s="38" t="inlineStr">
         <is>
           <t>・6/10　NSより通路天井下がり寸法の検討を指示
 ・6/25　SCより通路CH2350で納まるとの報告　
 ・7/5　NGKに説明し、了解を得た。</t>
         </is>
       </c>
-      <c r="M5" s="92" t="n"/>
-      <c r="N5" s="91" t="n">
+      <c r="M5" s="94" t="n"/>
+      <c r="N5" s="93" t="n">
         <v>45122</v>
       </c>
-      <c r="O5" s="40" t="n">
+      <c r="O5" s="39" t="n">
         <v>45112</v>
       </c>
-      <c r="P5" s="41" t="inlineStr">
+      <c r="P5" s="40" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A6" s="67" t="n">
+    <row r="6" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="68" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C6" s="68" t="n"/>
-      <c r="D6" s="68" t="n"/>
-      <c r="E6" s="68" t="n"/>
-      <c r="F6" s="68" t="n"/>
-      <c r="G6" s="68" t="n"/>
-      <c r="H6" s="93" t="n">
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="G6" s="19" t="n"/>
+      <c r="H6" s="95" t="n">
         <v>46283</v>
       </c>
-      <c r="I6" s="94" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="J6" s="71" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>着工は11月だが物決めは9～10月から始める必要があるため、物決めスケジュールを提示すること</t>
         </is>
       </c>
-      <c r="K6" s="94" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="L6" s="95" t="inlineStr">
+      <c r="L6" s="79" t="inlineStr">
         <is>
           <t>・9/18 第1回定例　NSより物決めスケジュールの提示を指示
 ・同　SCより工程プロモーションを後日送付のうえ説明すると回答</t>
         </is>
       </c>
       <c r="M6" s="96" t="n"/>
-      <c r="N6" s="93" t="n"/>
+      <c r="N6" s="95" t="n"/>
       <c r="O6" s="97" t="n"/>
-      <c r="P6" s="98" t="n"/>
-    </row>
-    <row r="7" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A7" s="67" t="n">
+      <c r="P6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="99" t="n"/>
-      <c r="C7" s="99" t="n"/>
-      <c r="D7" s="99" t="n"/>
-      <c r="E7" s="99" t="n"/>
-      <c r="F7" s="99" t="n"/>
-      <c r="G7" s="99" t="n"/>
-      <c r="H7" s="100" t="n">
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="25" t="n"/>
+      <c r="D7" s="25" t="n"/>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="25" t="n"/>
+      <c r="G7" s="25" t="n"/>
+      <c r="H7" s="98" t="n">
         <v>46283</v>
       </c>
-      <c r="I7" s="101" t="inlineStr">
+      <c r="I7" s="71" t="inlineStr">
         <is>
           <t>SJ</t>
         </is>
       </c>
-      <c r="J7" s="102" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3月15日の卒業式時点での出来栄え（食堂・外構）を意識してほしい</t>
         </is>
       </c>
-      <c r="K7" s="101" t="inlineStr">
+      <c r="K7" s="71" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="L7" s="103" t="inlineStr">
+      <c r="L7" s="46" t="inlineStr">
         <is>
           <t>・9/18 第1回定例　SJより要望
 ・同　SCより日付が近づいたら状況を説明すると回答</t>
         </is>
       </c>
-      <c r="M7" s="104" t="n"/>
-      <c r="N7" s="105" t="n"/>
-      <c r="O7" s="105" t="n"/>
-      <c r="P7" s="106" t="n"/>
+      <c r="M7" s="99" t="n"/>
+      <c r="N7" s="100" t="n"/>
+      <c r="O7" s="100" t="n"/>
+      <c r="P7" s="101" t="n"/>
       <c r="Q7" s="1" t="n"/>
     </row>
-    <row r="8" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A8" s="67" t="n">
+    <row r="8" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="99" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C8" s="99" t="n"/>
-      <c r="D8" s="99" t="n"/>
-      <c r="E8" s="99" t="n"/>
-      <c r="F8" s="99" t="inlineStr">
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G8" s="99" t="n"/>
-      <c r="H8" s="100" t="n">
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="98" t="n">
         <v>46283</v>
       </c>
-      <c r="I8" s="101" t="inlineStr">
+      <c r="I8" s="71" t="inlineStr">
         <is>
           <t>SJ</t>
         </is>
       </c>
-      <c r="J8" s="102" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>キャンパスヤードのウッドデッキ据付後、排水溝の掃除がしにくくなるのではないか</t>
         </is>
       </c>
-      <c r="K8" s="101" t="inlineStr">
+      <c r="K8" s="71" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L8" s="103" t="inlineStr">
+      <c r="L8" s="46" t="inlineStr">
         <is>
           <t>・9/18 第1回定例　SJより懸念提示
 ・同　NSよりウッドデッキの点検口が充分か確認すると回答</t>
         </is>
       </c>
-      <c r="M8" s="104" t="n"/>
-      <c r="N8" s="105" t="n"/>
-      <c r="O8" s="105" t="n"/>
-      <c r="P8" s="106" t="n"/>
+      <c r="M8" s="99" t="n"/>
+      <c r="N8" s="100" t="n"/>
+      <c r="O8" s="100" t="n"/>
+      <c r="P8" s="101" t="n"/>
       <c r="Q8" s="1" t="n"/>
     </row>
-    <row r="9" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A9" s="107" t="n">
+    <row r="9" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A9" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="108" t="n"/>
-      <c r="C9" s="108" t="n"/>
-      <c r="D9" s="108" t="n"/>
-      <c r="E9" s="108" t="n"/>
-      <c r="F9" s="108" t="inlineStr">
+      <c r="B9" s="48" t="n"/>
+      <c r="C9" s="48" t="n"/>
+      <c r="D9" s="48" t="n"/>
+      <c r="E9" s="48" t="n"/>
+      <c r="F9" s="48" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G9" s="108" t="n"/>
-      <c r="H9" s="109" t="n">
+      <c r="G9" s="48" t="n"/>
+      <c r="H9" s="102" t="n">
         <v>46283</v>
       </c>
-      <c r="I9" s="110" t="inlineStr">
+      <c r="I9" s="50" t="inlineStr">
         <is>
           <t>SJ</t>
         </is>
       </c>
-      <c r="J9" s="111" t="inlineStr">
+      <c r="J9" s="51" t="inlineStr">
         <is>
           <t>食堂出入口の階段下の側溝に水が溜まるので、合わせて確認してほしい</t>
         </is>
       </c>
-      <c r="K9" s="110" t="inlineStr">
+      <c r="K9" s="50" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L9" s="112" t="inlineStr">
+      <c r="L9" s="80" t="inlineStr">
         <is>
           <t>・9/18 第1回定例　SJより依頼
 ・同　NS承知</t>
         </is>
       </c>
-      <c r="M9" s="113" t="n"/>
-      <c r="N9" s="114" t="n"/>
-      <c r="O9" s="114" t="n"/>
-      <c r="P9" s="115" t="n"/>
+      <c r="M9" s="103" t="n"/>
+      <c r="N9" s="104" t="n"/>
+      <c r="O9" s="104" t="n"/>
+      <c r="P9" s="105" t="n"/>
       <c r="Q9" s="1" t="n"/>
     </row>
-    <row r="10" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A10" s="67" t="n">
+    <row r="10" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A10" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="68" t="n"/>
-      <c r="C10" s="68" t="n"/>
-      <c r="D10" s="68" t="n"/>
-      <c r="E10" s="68" t="n"/>
-      <c r="F10" s="68" t="n"/>
-      <c r="G10" s="68" t="n"/>
-      <c r="H10" s="93" t="n">
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="95" t="n">
         <v>46283</v>
       </c>
-      <c r="I10" s="70" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="J10" s="71" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>外構はコンサル業務契約のため、SCからSJへ直接承認を取るプロセスとなる。承認方法等を決めておくこと</t>
         </is>
       </c>
-      <c r="K10" s="101" t="inlineStr">
+      <c r="K10" s="71" t="inlineStr">
         <is>
           <t>SC
 SJ</t>
         </is>
       </c>
-      <c r="L10" s="103" t="inlineStr">
+      <c r="L10" s="46" t="inlineStr">
         <is>
           <t>・9/18 第1回定例　NSより連絡（食堂改修は監理業務、外構はコンサル業務）
 ・同　SC承知</t>
         </is>
       </c>
-      <c r="M10" s="116" t="n"/>
-      <c r="N10" s="93" t="n"/>
+      <c r="M10" s="106" t="n"/>
+      <c r="N10" s="95" t="n"/>
       <c r="O10" s="97" t="n"/>
-      <c r="P10" s="98" t="n"/>
+      <c r="P10" s="24" t="n"/>
       <c r="Q10" s="1" t="n"/>
     </row>
-    <row r="11" ht="49" customFormat="1" customHeight="1" s="82">
-      <c r="A11" s="67" t="n">
+    <row r="11" ht="49.05" customFormat="1" customHeight="1" s="78">
+      <c r="A11" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="68" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="68" t="n"/>
-      <c r="E11" s="68" t="n"/>
-      <c r="F11" s="68" t="n"/>
-      <c r="G11" s="68" t="n"/>
-      <c r="H11" s="93" t="n">
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="95" t="n">
         <v>46283</v>
       </c>
-      <c r="I11" s="70" t="inlineStr">
+      <c r="I11" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J11" s="71" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>アスベスト含有建材事前調査を10月初旬に実施予定</t>
         </is>
       </c>
-      <c r="K11" s="101" t="inlineStr">
+      <c r="K11" s="71" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="L11" s="103" t="inlineStr">
+      <c r="L11" s="46" t="inlineStr">
         <is>
           <t>・9/18 第1回定例　SCより報告
 ・同　SJよりアスベストは予算補正があるので早めに情報をあげるよう指示
 ・同　SC承知</t>
         </is>
       </c>
-      <c r="M11" s="116" t="n"/>
-      <c r="N11" s="93" t="n"/>
+      <c r="M11" s="106" t="n"/>
+      <c r="N11" s="95" t="n"/>
       <c r="O11" s="97" t="n"/>
-      <c r="P11" s="98" t="n"/>
+      <c r="P11" s="24" t="n"/>
       <c r="Q11" s="1" t="n"/>
     </row>
-    <row r="12" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A12" s="67" t="n">
+    <row r="12" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A12" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="68" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="68" t="n"/>
-      <c r="E12" s="68" t="n"/>
-      <c r="F12" s="68" t="n"/>
-      <c r="G12" s="68" t="n"/>
-      <c r="H12" s="93" t="n">
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="95" t="n">
         <v>46283</v>
       </c>
-      <c r="I12" s="70" t="inlineStr">
+      <c r="I12" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J12" s="71" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>2027年3月23日～26日の学生健診に影響のないよう工事を調整する</t>
         </is>
       </c>
-      <c r="K12" s="101" t="inlineStr">
+      <c r="K12" s="71" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="L12" s="103" t="inlineStr">
+      <c r="L12" s="46" t="inlineStr">
         <is>
           <t>・9/18 第1回定例　SCより承知した旨報告。今後調整</t>
         </is>
       </c>
-      <c r="M12" s="116" t="n"/>
-      <c r="N12" s="93" t="n"/>
+      <c r="M12" s="106" t="n"/>
+      <c r="N12" s="95" t="n"/>
       <c r="O12" s="97" t="n"/>
-      <c r="P12" s="98" t="n"/>
+      <c r="P12" s="24" t="n"/>
       <c r="Q12" s="1" t="n"/>
     </row>
-    <row r="13" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A13" s="107" t="n">
+    <row r="13" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A13" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="117" t="n"/>
-      <c r="C13" s="117" t="n"/>
-      <c r="D13" s="117" t="n"/>
-      <c r="E13" s="117" t="n"/>
-      <c r="F13" s="117" t="n"/>
-      <c r="G13" s="117" t="n"/>
-      <c r="H13" s="109" t="n">
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="102" t="n">
         <v>46283</v>
       </c>
-      <c r="I13" s="118" t="inlineStr">
+      <c r="I13" s="53" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J13" s="111" t="inlineStr">
+      <c r="J13" s="51" t="inlineStr">
         <is>
           <t>キャンパスヤード内でキッチンカー営業中。工事車両の出入りがあるため配置場所を調整する</t>
         </is>
       </c>
-      <c r="K13" s="119" t="inlineStr">
+      <c r="K13" s="54" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="L13" s="112" t="inlineStr">
+      <c r="L13" s="80" t="inlineStr">
         <is>
           <t>・9/18 第1回定例　SCより報告
 ・9/30　現地にて学生課・業者と打合せ予定</t>
         </is>
       </c>
-      <c r="M13" s="120" t="n"/>
-      <c r="N13" s="109" t="n">
+      <c r="M13" s="107" t="n"/>
+      <c r="N13" s="102" t="n">
         <v>46295</v>
       </c>
-      <c r="O13" s="114" t="n"/>
-      <c r="P13" s="115" t="n"/>
+      <c r="O13" s="104" t="n"/>
+      <c r="P13" s="105" t="n"/>
       <c r="Q13" s="1" t="n"/>
     </row>
-    <row r="14" ht="88" customFormat="1" customHeight="1" s="82">
-      <c r="A14" s="67" t="n">
+    <row r="14" ht="88.05" customFormat="1" customHeight="1" s="78">
+      <c r="A14" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="68" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="68" t="n"/>
-      <c r="E14" s="68" t="n"/>
-      <c r="F14" s="68" t="n"/>
-      <c r="G14" s="68" t="n"/>
-      <c r="H14" s="93" t="n">
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I14" s="70" t="inlineStr">
+      <c r="I14" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J14" s="121" t="inlineStr">
+      <c r="J14" s="81" t="inlineStr">
         <is>
           <t>床タイルの決定
 ・織部製陶4色MIX：提出タイルでの承認、接着剤色（グレー）、床目地色（M-2／M-3）、目地巾（5mmは施工不可のため8mmとしたい）
 ・名古屋モザイク アイスランド：タイル決定、ICE-10・20の単色かMIXか、目地色（M-2／M-3）</t>
         </is>
       </c>
-      <c r="K14" s="101" t="inlineStr">
+      <c r="K14" s="71" t="inlineStr">
         <is>
           <t>NS
 SJ</t>
         </is>
       </c>
-      <c r="L14" s="103" t="inlineStr">
+      <c r="L14" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SCより決定依頼</t>
         </is>
       </c>
-      <c r="M14" s="116" t="n"/>
-      <c r="N14" s="93" t="n"/>
+      <c r="M14" s="106" t="n"/>
+      <c r="N14" s="95" t="n"/>
       <c r="O14" s="97" t="n"/>
-      <c r="P14" s="98" t="n"/>
+      <c r="P14" s="24" t="n"/>
       <c r="Q14" s="1" t="n"/>
     </row>
-    <row r="15" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A15" s="67" t="n">
+    <row r="15" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A15" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="68" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C15" s="68" t="n"/>
-      <c r="D15" s="68" t="n"/>
-      <c r="E15" s="68" t="n"/>
-      <c r="F15" s="68" t="n"/>
-      <c r="G15" s="68" t="n"/>
-      <c r="H15" s="93" t="n">
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I15" s="70" t="inlineStr">
+      <c r="I15" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J15" s="71" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>SG1（スチール片開きガラリ）の取替理由の確認。既設と同仕様の納まりでよいか</t>
         </is>
       </c>
-      <c r="K15" s="94" t="inlineStr">
+      <c r="K15" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L15" s="103" t="inlineStr">
+      <c r="L15" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SCより質疑</t>
         </is>
       </c>
       <c r="M15" s="96" t="n"/>
-      <c r="N15" s="93" t="n"/>
+      <c r="N15" s="95" t="n"/>
       <c r="O15" s="97" t="n"/>
-      <c r="P15" s="98" t="n"/>
+      <c r="P15" s="24" t="n"/>
       <c r="Q15" s="1" t="n"/>
     </row>
-    <row r="16" ht="49" customFormat="1" customHeight="1" s="82">
-      <c r="A16" s="67" t="n">
+    <row r="16" ht="49.05" customFormat="1" customHeight="1" s="78">
+      <c r="A16" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="68" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C16" s="68" t="n"/>
-      <c r="D16" s="68" t="inlineStr">
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="E16" s="68" t="n"/>
-      <c r="F16" s="68" t="n"/>
-      <c r="G16" s="68" t="n"/>
-      <c r="H16" s="93" t="n">
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I16" s="70" t="inlineStr">
+      <c r="I16" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J16" s="71" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>AD1（意匠図1-18）のセンサーに天井埋込と無目取付の表記がある。天井センサーはサッシ面から300以上離す必要があり光天井と干渉の恐れ</t>
         </is>
       </c>
-      <c r="K16" s="94" t="inlineStr">
+      <c r="K16" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L16" s="103" t="inlineStr">
+      <c r="L16" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SCより質疑。今後検討が必要
 ・一旦、図面は無目付センサーで作図する</t>
         </is>
       </c>
       <c r="M16" s="96" t="n"/>
-      <c r="N16" s="93" t="n"/>
+      <c r="N16" s="95" t="n"/>
       <c r="O16" s="97" t="n"/>
-      <c r="P16" s="98" t="n"/>
+      <c r="P16" s="24" t="n"/>
       <c r="Q16" s="1" t="n"/>
     </row>
-    <row r="17" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A17" s="67" t="n">
+    <row r="17" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A17" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="68" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C17" s="68" t="n"/>
-      <c r="D17" s="68" t="n"/>
-      <c r="E17" s="68" t="n"/>
-      <c r="F17" s="68" t="n"/>
-      <c r="G17" s="68" t="n"/>
-      <c r="H17" s="93" t="n">
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I17" s="70" t="inlineStr">
+      <c r="I17" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J17" s="71" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>AD1の石取合い：建具入替のためエントランス側の石をカットまたは張り直す必要あり（割れのリスク有り）</t>
         </is>
       </c>
-      <c r="K17" s="94" t="inlineStr">
+      <c r="K17" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L17" s="103" t="inlineStr">
+      <c r="L17" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SC（生技）より、石を大きめにカットし見切金物を入れる納まりを提案（現場にて確認）</t>
         </is>
       </c>
       <c r="M17" s="96" t="n"/>
-      <c r="N17" s="93" t="n"/>
+      <c r="N17" s="95" t="n"/>
       <c r="O17" s="97" t="n"/>
-      <c r="P17" s="98" t="n"/>
+      <c r="P17" s="24" t="n"/>
       <c r="Q17" s="1" t="n"/>
     </row>
-    <row r="18" ht="49" customFormat="1" customHeight="1" s="82">
-      <c r="A18" s="67" t="n">
+    <row r="18" ht="49.05" customFormat="1" customHeight="1" s="78">
+      <c r="A18" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="68" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C18" s="68" t="n"/>
-      <c r="D18" s="68" t="n"/>
-      <c r="E18" s="68" t="n"/>
-      <c r="F18" s="68" t="n"/>
-      <c r="G18" s="68" t="n"/>
-      <c r="H18" s="93" t="n">
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I18" s="70" t="inlineStr">
+      <c r="I18" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J18" s="71" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>SSD（自動ドア）の色・艶の指示。色合わせが困難なためステンレスHLでの検討も依頼（外部アルミサッシはステンカラー）</t>
         </is>
       </c>
-      <c r="K18" s="94" t="inlineStr">
+      <c r="K18" s="21" t="inlineStr">
         <is>
           <t>NS
 SJ</t>
         </is>
       </c>
-      <c r="L18" s="103" t="inlineStr">
+      <c r="L18" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　見本提出、現場にて確認
 ・SC（生技）より製作納期80日を考慮し、現場取付日の後送りまたは現場塗装を提案。内外塗装範囲の指示を依頼</t>
         </is>
       </c>
       <c r="M18" s="96" t="n"/>
-      <c r="N18" s="93" t="n"/>
+      <c r="N18" s="95" t="n"/>
       <c r="O18" s="97" t="n"/>
-      <c r="P18" s="98" t="n"/>
+      <c r="P18" s="24" t="n"/>
       <c r="Q18" s="1" t="n"/>
     </row>
-    <row r="19" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A19" s="67" t="n">
+    <row r="19" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A19" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="68" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C19" s="68" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="D19" s="68" t="n"/>
-      <c r="E19" s="68" t="n"/>
-      <c r="F19" s="68" t="n"/>
-      <c r="G19" s="68" t="n"/>
-      <c r="H19" s="93" t="n">
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I19" s="70" t="inlineStr">
+      <c r="I19" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J19" s="71" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>SSD取付固定：火無工法にて既設耐風梁にビス固定でよいか</t>
         </is>
       </c>
-      <c r="K19" s="94" t="inlineStr">
+      <c r="K19" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L19" s="103" t="inlineStr">
+      <c r="L19" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SC（生技）より、現場運用図の既存耐風梁は鉄骨ではなく建具部材であり、ビス固定で問題ないと考える旨説明</t>
         </is>
       </c>
       <c r="M19" s="96" t="n"/>
-      <c r="N19" s="93" t="n"/>
+      <c r="N19" s="95" t="n"/>
       <c r="O19" s="97" t="n"/>
-      <c r="P19" s="98" t="n"/>
+      <c r="P19" s="24" t="n"/>
       <c r="Q19" s="1" t="n"/>
     </row>
-    <row r="20" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A20" s="67" t="n">
+    <row r="20" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A20" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="68" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C20" s="68" t="n"/>
-      <c r="D20" s="68" t="n"/>
-      <c r="E20" s="68" t="n"/>
-      <c r="F20" s="68" t="n"/>
-      <c r="G20" s="68" t="n"/>
-      <c r="H20" s="93" t="n">
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I20" s="70" t="inlineStr">
+      <c r="I20" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J20" s="71" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>アイカ モルタルアートのサンプル作成のため、カタログより色を選定してほしい</t>
         </is>
       </c>
-      <c r="K20" s="94" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
         <is>
           <t>NS
 SJ</t>
         </is>
       </c>
-      <c r="L20" s="103" t="inlineStr">
+      <c r="L20" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SCより依頼</t>
         </is>
       </c>
       <c r="M20" s="96" t="n"/>
-      <c r="N20" s="93" t="n"/>
+      <c r="N20" s="95" t="n"/>
       <c r="O20" s="97" t="n"/>
-      <c r="P20" s="98" t="n"/>
+      <c r="P20" s="24" t="n"/>
       <c r="Q20" s="1" t="n"/>
     </row>
-    <row r="21" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A21" s="67" t="n">
+    <row r="21" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A21" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="68" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C21" s="68" t="n"/>
-      <c r="D21" s="68" t="n"/>
-      <c r="E21" s="68" t="n"/>
-      <c r="F21" s="68" t="n"/>
-      <c r="G21" s="68" t="n"/>
-      <c r="H21" s="93" t="n">
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I21" s="70" t="inlineStr">
+      <c r="I21" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J21" s="71" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>吸音ルーバーの固定方法確認（ASタイプのZ金物20mmが標準品）、色サンプル作成用の日塗工品番指示（既製品は白）</t>
         </is>
       </c>
-      <c r="K21" s="94" t="inlineStr">
+      <c r="K21" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L21" s="103" t="inlineStr">
+      <c r="L21" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SCより確認・依頼（別紙参照）</t>
         </is>
       </c>
       <c r="M21" s="96" t="n"/>
-      <c r="N21" s="93" t="n"/>
+      <c r="N21" s="95" t="n"/>
       <c r="O21" s="97" t="n"/>
-      <c r="P21" s="98" t="n"/>
+      <c r="P21" s="24" t="n"/>
       <c r="Q21" s="1" t="n"/>
     </row>
-    <row r="22" ht="75" customFormat="1" customHeight="1" s="82">
-      <c r="A22" s="67" t="n">
+    <row r="22" ht="75" customFormat="1" customHeight="1" s="78">
+      <c r="A22" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="68" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C22" s="68" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="D22" s="68" t="n"/>
-      <c r="E22" s="68" t="n"/>
-      <c r="F22" s="68" t="n"/>
-      <c r="G22" s="68" t="n"/>
-      <c r="H22" s="93" t="n">
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I22" s="70" t="inlineStr">
+      <c r="I22" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J22" s="71" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>吸音ルーバーの納まり
 ①割付基準：定尺2970mm、ジョイント2mm
@@ -1930,49 +1880,49 @@
 ④天井点検口の納まり</t>
         </is>
       </c>
-      <c r="K22" s="94" t="inlineStr">
+      <c r="K22" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L22" s="103" t="inlineStr">
+      <c r="L22" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SC（生技）より、①検討図作成、②クランクに合わせたルーバー形状変更、③天端を下げ塗装仕上げ（タイルカーペットではなく）を提案。④は他現場の参考納まりの教示を依頼</t>
         </is>
       </c>
       <c r="M22" s="96" t="n"/>
-      <c r="N22" s="93" t="n"/>
+      <c r="N22" s="95" t="n"/>
       <c r="O22" s="97" t="n"/>
-      <c r="P22" s="98" t="n"/>
+      <c r="P22" s="24" t="n"/>
       <c r="Q22" s="3" t="n"/>
     </row>
-    <row r="23" ht="88" customFormat="1" customHeight="1" s="82">
-      <c r="A23" s="67" t="n">
+    <row r="23" ht="88.05" customFormat="1" customHeight="1" s="78">
+      <c r="A23" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="68" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C23" s="68" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="D23" s="68" t="n"/>
-      <c r="E23" s="68" t="n"/>
-      <c r="F23" s="68" t="n"/>
-      <c r="G23" s="68" t="n"/>
-      <c r="H23" s="93" t="n">
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I23" s="70" t="inlineStr">
+      <c r="I23" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J23" s="71" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>家具の転倒防止
 ①窓際カウンター（食堂西・東）：図面FBt12、SC検討中：角パイプ・控え・BK可否、ピッチ
@@ -1980,231 +1930,231 @@
 ③下膳台：コの字で安定</t>
         </is>
       </c>
-      <c r="K23" s="94" t="inlineStr">
+      <c r="K23" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L23" s="103" t="inlineStr">
+      <c r="L23" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SC（生技）より確認依頼</t>
         </is>
       </c>
       <c r="M23" s="96" t="n"/>
-      <c r="N23" s="93" t="n"/>
+      <c r="N23" s="95" t="n"/>
       <c r="O23" s="97" t="n"/>
-      <c r="P23" s="98" t="n"/>
+      <c r="P23" s="24" t="n"/>
       <c r="Q23" s="1" t="n"/>
     </row>
-    <row r="24" ht="49" customFormat="1" customHeight="1" s="82">
-      <c r="A24" s="67" t="n">
+    <row r="24" ht="49.05" customFormat="1" customHeight="1" s="78">
+      <c r="A24" s="18" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="68" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C24" s="68" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="D24" s="68" t="n"/>
-      <c r="E24" s="68" t="n"/>
-      <c r="F24" s="68" t="n"/>
-      <c r="G24" s="68" t="n"/>
-      <c r="H24" s="93" t="n">
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I24" s="70" t="inlineStr">
+      <c r="I24" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J24" s="71" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>ハンガードア（CH3150）
 ①床側固定（タイル固定か躯体アンカーか、金物仕様）
 ②上部下地（LGS可否検討中。鉄骨下地の場合は追加）</t>
         </is>
       </c>
-      <c r="K24" s="94" t="inlineStr">
+      <c r="K24" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L24" s="103" t="inlineStr">
+      <c r="L24" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SCにて検討中</t>
         </is>
       </c>
       <c r="M24" s="96" t="n"/>
-      <c r="N24" s="93" t="n"/>
+      <c r="N24" s="95" t="n"/>
       <c r="O24" s="97" t="n"/>
-      <c r="P24" s="98" t="n"/>
+      <c r="P24" s="24" t="n"/>
       <c r="Q24" s="1" t="n"/>
     </row>
-    <row r="25" ht="49" customFormat="1" customHeight="1" s="82">
-      <c r="A25" s="67" t="n">
+    <row r="25" ht="49.05" customFormat="1" customHeight="1" s="78">
+      <c r="A25" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="68" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C25" s="68" t="n"/>
-      <c r="D25" s="68" t="n"/>
-      <c r="E25" s="68" t="n"/>
-      <c r="F25" s="68" t="n"/>
-      <c r="G25" s="68" t="n"/>
-      <c r="H25" s="93" t="n">
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I25" s="70" t="inlineStr">
+      <c r="I25" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J25" s="71" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>床モルタルアート（t2.5）の仕上げレベル：取合いレベルを+2.5とするか、建具廻り床タイルを1m程度剥がしてなじませるか</t>
         </is>
       </c>
-      <c r="K25" s="94" t="inlineStr">
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>NS
 SJ</t>
         </is>
       </c>
-      <c r="L25" s="103" t="inlineStr">
+      <c r="L25" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SC（生技）より指示依頼。追加になるが後者を推奨</t>
         </is>
       </c>
       <c r="M25" s="96" t="n"/>
-      <c r="N25" s="93" t="n"/>
+      <c r="N25" s="95" t="n"/>
       <c r="O25" s="97" t="n"/>
-      <c r="P25" s="98" t="n"/>
+      <c r="P25" s="24" t="n"/>
       <c r="Q25" s="1" t="n"/>
     </row>
-    <row r="26" ht="49" customFormat="1" customHeight="1" s="82">
-      <c r="A26" s="67" t="n">
+    <row r="26" ht="49.05" customFormat="1" customHeight="1" s="78">
+      <c r="A26" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="68" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C26" s="68" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="D26" s="68" t="n"/>
-      <c r="E26" s="68" t="n"/>
-      <c r="F26" s="68" t="n"/>
-      <c r="G26" s="68" t="n"/>
-      <c r="H26" s="93" t="n">
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I26" s="70" t="inlineStr">
+      <c r="I26" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J26" s="71" t="inlineStr">
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>鋼製床（東洋工業：JIS規格品ではない）
 ①採用可否・必要性能・確認資料、設計承認の状況
 ②点検口の要否・設置数（H800床下は人が入れない）</t>
         </is>
       </c>
-      <c r="K26" s="94" t="inlineStr">
+      <c r="K26" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L26" s="103" t="inlineStr">
+      <c r="L26" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SC（生技）より確認依頼（打合図参照）</t>
         </is>
       </c>
       <c r="M26" s="96" t="n"/>
-      <c r="N26" s="93" t="n"/>
+      <c r="N26" s="95" t="n"/>
       <c r="O26" s="97" t="n"/>
-      <c r="P26" s="98" t="n"/>
+      <c r="P26" s="24" t="n"/>
       <c r="Q26" s="1" t="n"/>
     </row>
-    <row r="27" ht="40" customFormat="1" customHeight="1" s="82">
-      <c r="A27" s="67" t="n">
+    <row r="27" ht="40.05" customFormat="1" customHeight="1" s="78">
+      <c r="A27" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="68" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C27" s="68" t="n"/>
-      <c r="D27" s="68" t="n"/>
-      <c r="E27" s="68" t="n"/>
-      <c r="F27" s="68" t="n"/>
-      <c r="G27" s="68" t="n"/>
-      <c r="H27" s="93" t="n">
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I27" s="70" t="inlineStr">
+      <c r="I27" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J27" s="71" t="inlineStr">
+      <c r="J27" s="22" t="inlineStr">
         <is>
           <t>カウンター席オークUC乱張りの方向（食堂西：現場運用図・パースは横張り、食堂東：パースは縦張り）</t>
         </is>
       </c>
-      <c r="K27" s="94" t="inlineStr">
+      <c r="K27" s="21" t="inlineStr">
         <is>
           <t>NS
 SJ</t>
         </is>
       </c>
-      <c r="L27" s="103" t="inlineStr">
+      <c r="L27" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SC（生技）より指示依頼</t>
         </is>
       </c>
       <c r="M27" s="96" t="n"/>
-      <c r="N27" s="93" t="n"/>
+      <c r="N27" s="95" t="n"/>
       <c r="O27" s="97" t="n"/>
-      <c r="P27" s="98" t="n"/>
+      <c r="P27" s="24" t="n"/>
       <c r="Q27" s="1" t="n"/>
     </row>
-    <row r="28" ht="75" customFormat="1" customHeight="1" s="82">
-      <c r="A28" s="67" t="n">
+    <row r="28" ht="75" customFormat="1" customHeight="1" s="78">
+      <c r="A28" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="68" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C28" s="68" t="n"/>
-      <c r="D28" s="68" t="n"/>
-      <c r="E28" s="68" t="n"/>
-      <c r="F28" s="68" t="n"/>
-      <c r="G28" s="68" t="n"/>
-      <c r="H28" s="93" t="n">
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="19" t="n"/>
+      <c r="H28" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="I28" s="70" t="inlineStr">
+      <c r="I28" s="31" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J28" s="71" t="inlineStr">
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>図面・計画書リスト
 ①建具の発注納期（納期が迫っている。施工時期か現場塗装で調整必要）
@@ -2212,23 +2162,23 @@
 ③竣工図（改修後の建築物全体図（平面図））</t>
         </is>
       </c>
-      <c r="K28" s="94" t="inlineStr">
+      <c r="K28" s="21" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L28" s="103" t="inlineStr">
+      <c r="L28" s="46" t="inlineStr">
         <is>
           <t>・9/28 第1回分科会　SC（生技）より確認（box内資料参照）</t>
         </is>
       </c>
       <c r="M28" s="96" t="n"/>
-      <c r="N28" s="93" t="n"/>
+      <c r="N28" s="95" t="n"/>
       <c r="O28" s="97" t="n"/>
-      <c r="P28" s="98" t="n"/>
+      <c r="P28" s="24" t="n"/>
       <c r="Q28" s="1" t="n"/>
     </row>
-    <row r="29" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="29" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A29" s="18" t="n"/>
       <c r="B29" s="19" t="n"/>
       <c r="C29" s="19" t="n"/>
@@ -2236,18 +2186,18 @@
       <c r="E29" s="19" t="n"/>
       <c r="F29" s="19" t="n"/>
       <c r="G29" s="19" t="n"/>
-      <c r="H29" s="122" t="n"/>
-      <c r="I29" s="32" t="n"/>
+      <c r="H29" s="95" t="n"/>
+      <c r="I29" s="31" t="n"/>
       <c r="J29" s="22" t="n"/>
       <c r="K29" s="21" t="n"/>
-      <c r="L29" s="33" t="n"/>
-      <c r="M29" s="123" t="n"/>
-      <c r="N29" s="122" t="n"/>
+      <c r="L29" s="32" t="n"/>
+      <c r="M29" s="96" t="n"/>
+      <c r="N29" s="95" t="n"/>
       <c r="O29" s="23" t="n"/>
       <c r="P29" s="24" t="n"/>
       <c r="Q29" s="1" t="n"/>
     </row>
-    <row r="30" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="30" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A30" s="18" t="n"/>
       <c r="B30" s="19" t="n"/>
       <c r="C30" s="19" t="n"/>
@@ -2255,18 +2205,18 @@
       <c r="E30" s="19" t="n"/>
       <c r="F30" s="19" t="n"/>
       <c r="G30" s="19" t="n"/>
-      <c r="H30" s="122" t="n"/>
-      <c r="I30" s="32" t="n"/>
+      <c r="H30" s="95" t="n"/>
+      <c r="I30" s="31" t="n"/>
       <c r="J30" s="22" t="n"/>
       <c r="K30" s="21" t="n"/>
-      <c r="L30" s="33" t="n"/>
-      <c r="M30" s="123" t="n"/>
-      <c r="N30" s="122" t="n"/>
+      <c r="L30" s="32" t="n"/>
+      <c r="M30" s="96" t="n"/>
+      <c r="N30" s="95" t="n"/>
       <c r="O30" s="23" t="n"/>
       <c r="P30" s="24" t="n"/>
       <c r="Q30" s="1" t="n"/>
     </row>
-    <row r="31" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="31" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A31" s="18" t="n"/>
       <c r="B31" s="19" t="n"/>
       <c r="C31" s="19" t="n"/>
@@ -2274,18 +2224,18 @@
       <c r="E31" s="19" t="n"/>
       <c r="F31" s="19" t="n"/>
       <c r="G31" s="19" t="n"/>
-      <c r="H31" s="122" t="n"/>
-      <c r="I31" s="32" t="n"/>
+      <c r="H31" s="95" t="n"/>
+      <c r="I31" s="31" t="n"/>
       <c r="J31" s="22" t="n"/>
       <c r="K31" s="21" t="n"/>
-      <c r="L31" s="33" t="n"/>
-      <c r="M31" s="123" t="n"/>
-      <c r="N31" s="122" t="n"/>
+      <c r="L31" s="32" t="n"/>
+      <c r="M31" s="96" t="n"/>
+      <c r="N31" s="95" t="n"/>
       <c r="O31" s="23" t="n"/>
       <c r="P31" s="24" t="n"/>
       <c r="Q31" s="1" t="n"/>
     </row>
-    <row r="32" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="32" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A32" s="18" t="n"/>
       <c r="B32" s="19" t="n"/>
       <c r="C32" s="19" t="n"/>
@@ -2293,18 +2243,18 @@
       <c r="E32" s="19" t="n"/>
       <c r="F32" s="19" t="n"/>
       <c r="G32" s="19" t="n"/>
-      <c r="H32" s="122" t="n"/>
-      <c r="I32" s="32" t="n"/>
+      <c r="H32" s="95" t="n"/>
+      <c r="I32" s="31" t="n"/>
       <c r="J32" s="22" t="n"/>
       <c r="K32" s="21" t="n"/>
-      <c r="L32" s="33" t="n"/>
-      <c r="M32" s="123" t="n"/>
-      <c r="N32" s="122" t="n"/>
+      <c r="L32" s="32" t="n"/>
+      <c r="M32" s="96" t="n"/>
+      <c r="N32" s="95" t="n"/>
       <c r="O32" s="23" t="n"/>
       <c r="P32" s="24" t="n"/>
       <c r="Q32" s="1" t="n"/>
     </row>
-    <row r="33" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="33" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A33" s="18" t="n"/>
       <c r="B33" s="19" t="n"/>
       <c r="C33" s="19" t="n"/>
@@ -2312,18 +2262,18 @@
       <c r="E33" s="19" t="n"/>
       <c r="F33" s="19" t="n"/>
       <c r="G33" s="19" t="n"/>
-      <c r="H33" s="122" t="n"/>
-      <c r="I33" s="32" t="n"/>
+      <c r="H33" s="95" t="n"/>
+      <c r="I33" s="31" t="n"/>
       <c r="J33" s="22" t="n"/>
       <c r="K33" s="21" t="n"/>
-      <c r="L33" s="33" t="n"/>
-      <c r="M33" s="123" t="n"/>
-      <c r="N33" s="122" t="n"/>
+      <c r="L33" s="32" t="n"/>
+      <c r="M33" s="96" t="n"/>
+      <c r="N33" s="95" t="n"/>
       <c r="O33" s="23" t="n"/>
       <c r="P33" s="24" t="n"/>
       <c r="Q33" s="1" t="n"/>
     </row>
-    <row r="34" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="34" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A34" s="18" t="n"/>
       <c r="B34" s="19" t="n"/>
       <c r="C34" s="19" t="n"/>
@@ -2331,18 +2281,18 @@
       <c r="E34" s="19" t="n"/>
       <c r="F34" s="19" t="n"/>
       <c r="G34" s="19" t="n"/>
-      <c r="H34" s="122" t="n"/>
-      <c r="I34" s="32" t="n"/>
+      <c r="H34" s="95" t="n"/>
+      <c r="I34" s="31" t="n"/>
       <c r="J34" s="22" t="n"/>
       <c r="K34" s="21" t="n"/>
-      <c r="L34" s="33" t="n"/>
-      <c r="M34" s="123" t="n"/>
-      <c r="N34" s="122" t="n"/>
+      <c r="L34" s="32" t="n"/>
+      <c r="M34" s="96" t="n"/>
+      <c r="N34" s="95" t="n"/>
       <c r="O34" s="23" t="n"/>
       <c r="P34" s="24" t="n"/>
       <c r="Q34" s="1" t="n"/>
     </row>
-    <row r="35" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="35" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A35" s="18" t="n"/>
       <c r="B35" s="19" t="n"/>
       <c r="C35" s="19" t="n"/>
@@ -2350,18 +2300,18 @@
       <c r="E35" s="19" t="n"/>
       <c r="F35" s="19" t="n"/>
       <c r="G35" s="19" t="n"/>
-      <c r="H35" s="122" t="n"/>
-      <c r="I35" s="32" t="n"/>
+      <c r="H35" s="95" t="n"/>
+      <c r="I35" s="31" t="n"/>
       <c r="J35" s="22" t="n"/>
       <c r="K35" s="21" t="n"/>
-      <c r="L35" s="33" t="n"/>
-      <c r="M35" s="123" t="n"/>
-      <c r="N35" s="122" t="n"/>
+      <c r="L35" s="32" t="n"/>
+      <c r="M35" s="96" t="n"/>
+      <c r="N35" s="95" t="n"/>
       <c r="O35" s="23" t="n"/>
       <c r="P35" s="24" t="n"/>
       <c r="Q35" s="1" t="n"/>
     </row>
-    <row r="36" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="36" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A36" s="18" t="n"/>
       <c r="B36" s="19" t="n"/>
       <c r="C36" s="19" t="n"/>
@@ -2369,18 +2319,18 @@
       <c r="E36" s="19" t="n"/>
       <c r="F36" s="19" t="n"/>
       <c r="G36" s="19" t="n"/>
-      <c r="H36" s="122" t="n"/>
-      <c r="I36" s="32" t="n"/>
+      <c r="H36" s="95" t="n"/>
+      <c r="I36" s="31" t="n"/>
       <c r="J36" s="22" t="n"/>
       <c r="K36" s="21" t="n"/>
-      <c r="L36" s="33" t="n"/>
-      <c r="M36" s="123" t="n"/>
-      <c r="N36" s="122" t="n"/>
+      <c r="L36" s="32" t="n"/>
+      <c r="M36" s="96" t="n"/>
+      <c r="N36" s="95" t="n"/>
       <c r="O36" s="23" t="n"/>
       <c r="P36" s="24" t="n"/>
       <c r="Q36" s="1" t="n"/>
     </row>
-    <row r="37" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="37" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A37" s="18" t="n"/>
       <c r="B37" s="19" t="n"/>
       <c r="C37" s="19" t="n"/>
@@ -2388,18 +2338,18 @@
       <c r="E37" s="19" t="n"/>
       <c r="F37" s="19" t="n"/>
       <c r="G37" s="19" t="n"/>
-      <c r="H37" s="122" t="n"/>
-      <c r="I37" s="32" t="n"/>
+      <c r="H37" s="95" t="n"/>
+      <c r="I37" s="31" t="n"/>
       <c r="J37" s="22" t="n"/>
       <c r="K37" s="21" t="n"/>
-      <c r="L37" s="33" t="n"/>
-      <c r="M37" s="123" t="n"/>
-      <c r="N37" s="122" t="n"/>
+      <c r="L37" s="32" t="n"/>
+      <c r="M37" s="96" t="n"/>
+      <c r="N37" s="95" t="n"/>
       <c r="O37" s="23" t="n"/>
       <c r="P37" s="24" t="n"/>
       <c r="Q37" s="1" t="n"/>
     </row>
-    <row r="38" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="38" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A38" s="18" t="n"/>
       <c r="B38" s="19" t="n"/>
       <c r="C38" s="19" t="n"/>
@@ -2407,18 +2357,18 @@
       <c r="E38" s="19" t="n"/>
       <c r="F38" s="19" t="n"/>
       <c r="G38" s="19" t="n"/>
-      <c r="H38" s="122" t="n"/>
-      <c r="I38" s="32" t="n"/>
+      <c r="H38" s="95" t="n"/>
+      <c r="I38" s="31" t="n"/>
       <c r="J38" s="22" t="n"/>
       <c r="K38" s="21" t="n"/>
-      <c r="L38" s="33" t="n"/>
-      <c r="M38" s="123" t="n"/>
-      <c r="N38" s="122" t="n"/>
+      <c r="L38" s="32" t="n"/>
+      <c r="M38" s="96" t="n"/>
+      <c r="N38" s="95" t="n"/>
       <c r="O38" s="23" t="n"/>
       <c r="P38" s="24" t="n"/>
       <c r="Q38" s="1" t="n"/>
     </row>
-    <row r="39" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="39" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A39" s="18" t="n"/>
       <c r="B39" s="19" t="n"/>
       <c r="C39" s="19" t="n"/>
@@ -2426,18 +2376,18 @@
       <c r="E39" s="19" t="n"/>
       <c r="F39" s="19" t="n"/>
       <c r="G39" s="19" t="n"/>
-      <c r="H39" s="122" t="n"/>
-      <c r="I39" s="32" t="n"/>
+      <c r="H39" s="95" t="n"/>
+      <c r="I39" s="31" t="n"/>
       <c r="J39" s="22" t="n"/>
       <c r="K39" s="21" t="n"/>
-      <c r="L39" s="33" t="n"/>
-      <c r="M39" s="123" t="n"/>
-      <c r="N39" s="122" t="n"/>
+      <c r="L39" s="32" t="n"/>
+      <c r="M39" s="96" t="n"/>
+      <c r="N39" s="95" t="n"/>
       <c r="O39" s="23" t="n"/>
       <c r="P39" s="24" t="n"/>
       <c r="Q39" s="1" t="n"/>
     </row>
-    <row r="40" ht="80.09999999999999" customFormat="1" customHeight="1" s="82">
+    <row r="40" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A40" s="18" t="n"/>
       <c r="B40" s="19" t="n"/>
       <c r="C40" s="19" t="n"/>
@@ -2445,18 +2395,18 @@
       <c r="E40" s="19" t="n"/>
       <c r="F40" s="19" t="n"/>
       <c r="G40" s="19" t="n"/>
-      <c r="H40" s="122" t="n"/>
-      <c r="I40" s="32" t="n"/>
+      <c r="H40" s="95" t="n"/>
+      <c r="I40" s="31" t="n"/>
       <c r="J40" s="22" t="n"/>
       <c r="K40" s="21" t="n"/>
-      <c r="L40" s="33" t="n"/>
-      <c r="M40" s="123" t="n"/>
-      <c r="N40" s="122" t="n"/>
+      <c r="L40" s="32" t="n"/>
+      <c r="M40" s="96" t="n"/>
+      <c r="N40" s="95" t="n"/>
       <c r="O40" s="23" t="n"/>
       <c r="P40" s="24" t="n"/>
       <c r="Q40" s="1" t="n"/>
     </row>
-    <row r="41" ht="50.1" customFormat="1" customHeight="1" s="82">
+    <row r="41" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A41" s="18" t="n"/>
       <c r="B41" s="19" t="n"/>
       <c r="C41" s="19" t="n"/>
@@ -2464,18 +2414,18 @@
       <c r="E41" s="19" t="n"/>
       <c r="F41" s="19" t="n"/>
       <c r="G41" s="19" t="n"/>
-      <c r="H41" s="122" t="n"/>
-      <c r="I41" s="32" t="n"/>
+      <c r="H41" s="95" t="n"/>
+      <c r="I41" s="31" t="n"/>
       <c r="J41" s="22" t="n"/>
       <c r="K41" s="21" t="n"/>
-      <c r="L41" s="33" t="n"/>
-      <c r="M41" s="123" t="n"/>
-      <c r="N41" s="122" t="n"/>
+      <c r="L41" s="32" t="n"/>
+      <c r="M41" s="96" t="n"/>
+      <c r="N41" s="95" t="n"/>
       <c r="O41" s="23" t="n"/>
       <c r="P41" s="24" t="n"/>
       <c r="Q41" s="3" t="n"/>
     </row>
-    <row r="42" ht="50.1" customFormat="1" customHeight="1" s="82">
+    <row r="42" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A42" s="18" t="n"/>
       <c r="B42" s="19" t="n"/>
       <c r="C42" s="19" t="n"/>
@@ -2483,18 +2433,18 @@
       <c r="E42" s="19" t="n"/>
       <c r="F42" s="19" t="n"/>
       <c r="G42" s="19" t="n"/>
-      <c r="H42" s="122" t="n"/>
-      <c r="I42" s="32" t="n"/>
+      <c r="H42" s="95" t="n"/>
+      <c r="I42" s="31" t="n"/>
       <c r="J42" s="22" t="n"/>
       <c r="K42" s="21" t="n"/>
-      <c r="L42" s="33" t="n"/>
-      <c r="M42" s="123" t="n"/>
-      <c r="N42" s="122" t="n"/>
+      <c r="L42" s="32" t="n"/>
+      <c r="M42" s="96" t="n"/>
+      <c r="N42" s="95" t="n"/>
       <c r="O42" s="23" t="n"/>
       <c r="P42" s="24" t="n"/>
       <c r="Q42" s="1" t="n"/>
     </row>
-    <row r="43" ht="264" customFormat="1" customHeight="1" s="82">
+    <row r="43" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A43" s="18" t="n"/>
       <c r="B43" s="19" t="n"/>
       <c r="C43" s="19" t="n"/>
@@ -2502,17 +2452,17 @@
       <c r="E43" s="19" t="n"/>
       <c r="F43" s="19" t="n"/>
       <c r="G43" s="19" t="n"/>
-      <c r="H43" s="122" t="n"/>
-      <c r="I43" s="32" t="n"/>
+      <c r="H43" s="95" t="n"/>
+      <c r="I43" s="31" t="n"/>
       <c r="J43" s="22" t="n"/>
       <c r="K43" s="21" t="n"/>
-      <c r="L43" s="33" t="n"/>
-      <c r="M43" s="123" t="n"/>
-      <c r="N43" s="122" t="n"/>
+      <c r="L43" s="32" t="n"/>
+      <c r="M43" s="96" t="n"/>
+      <c r="N43" s="95" t="n"/>
       <c r="O43" s="23" t="n"/>
       <c r="P43" s="24" t="n"/>
     </row>
-    <row r="44" ht="133.5" customFormat="1" customHeight="1" s="82">
+    <row r="44" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A44" s="18" t="n"/>
       <c r="B44" s="19" t="n"/>
       <c r="C44" s="19" t="n"/>
@@ -2520,17 +2470,17 @@
       <c r="E44" s="19" t="n"/>
       <c r="F44" s="19" t="n"/>
       <c r="G44" s="19" t="n"/>
-      <c r="H44" s="122" t="n"/>
-      <c r="I44" s="32" t="n"/>
+      <c r="H44" s="95" t="n"/>
+      <c r="I44" s="31" t="n"/>
       <c r="J44" s="22" t="n"/>
       <c r="K44" s="21" t="n"/>
-      <c r="L44" s="33" t="n"/>
-      <c r="M44" s="123" t="n"/>
-      <c r="N44" s="122" t="n"/>
+      <c r="L44" s="32" t="n"/>
+      <c r="M44" s="96" t="n"/>
+      <c r="N44" s="95" t="n"/>
       <c r="O44" s="23" t="n"/>
       <c r="P44" s="24" t="n"/>
     </row>
-    <row r="45" ht="50.1" customFormat="1" customHeight="1" s="82">
+    <row r="45" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A45" s="18" t="n"/>
       <c r="B45" s="19" t="n"/>
       <c r="C45" s="19" t="n"/>
@@ -2538,17 +2488,17 @@
       <c r="E45" s="19" t="n"/>
       <c r="F45" s="19" t="n"/>
       <c r="G45" s="19" t="n"/>
-      <c r="H45" s="122" t="n"/>
-      <c r="I45" s="32" t="n"/>
+      <c r="H45" s="95" t="n"/>
+      <c r="I45" s="31" t="n"/>
       <c r="J45" s="22" t="n"/>
       <c r="K45" s="21" t="n"/>
-      <c r="L45" s="33" t="n"/>
-      <c r="M45" s="123" t="n"/>
-      <c r="N45" s="122" t="n"/>
+      <c r="L45" s="32" t="n"/>
+      <c r="M45" s="96" t="n"/>
+      <c r="N45" s="95" t="n"/>
       <c r="O45" s="23" t="n"/>
       <c r="P45" s="24" t="n"/>
     </row>
-    <row r="46" ht="79.5" customFormat="1" customHeight="1" s="82">
+    <row r="46" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A46" s="18" t="n"/>
       <c r="B46" s="19" t="n"/>
       <c r="C46" s="19" t="n"/>
@@ -2556,17 +2506,17 @@
       <c r="E46" s="19" t="n"/>
       <c r="F46" s="19" t="n"/>
       <c r="G46" s="19" t="n"/>
-      <c r="H46" s="122" t="n"/>
-      <c r="I46" s="32" t="n"/>
+      <c r="H46" s="95" t="n"/>
+      <c r="I46" s="31" t="n"/>
       <c r="J46" s="22" t="n"/>
       <c r="K46" s="21" t="n"/>
-      <c r="L46" s="33" t="n"/>
-      <c r="M46" s="123" t="n"/>
-      <c r="N46" s="122" t="n"/>
+      <c r="L46" s="32" t="n"/>
+      <c r="M46" s="96" t="n"/>
+      <c r="N46" s="95" t="n"/>
       <c r="O46" s="23" t="n"/>
       <c r="P46" s="24" t="n"/>
     </row>
-    <row r="47" ht="67.5" customFormat="1" customHeight="1" s="82">
+    <row r="47" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A47" s="18" t="n"/>
       <c r="B47" s="19" t="n"/>
       <c r="C47" s="19" t="n"/>
@@ -2574,17 +2524,17 @@
       <c r="E47" s="19" t="n"/>
       <c r="F47" s="19" t="n"/>
       <c r="G47" s="19" t="n"/>
-      <c r="H47" s="122" t="n"/>
-      <c r="I47" s="32" t="n"/>
+      <c r="H47" s="95" t="n"/>
+      <c r="I47" s="31" t="n"/>
       <c r="J47" s="22" t="n"/>
       <c r="K47" s="21" t="n"/>
-      <c r="L47" s="33" t="n"/>
-      <c r="M47" s="123" t="n"/>
-      <c r="N47" s="122" t="n"/>
+      <c r="L47" s="32" t="n"/>
+      <c r="M47" s="96" t="n"/>
+      <c r="N47" s="95" t="n"/>
       <c r="O47" s="23" t="n"/>
       <c r="P47" s="24" t="n"/>
     </row>
-    <row r="48" ht="200.7" customFormat="1" customHeight="1" s="82">
+    <row r="48" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A48" s="18" t="n"/>
       <c r="B48" s="19" t="n"/>
       <c r="C48" s="19" t="n"/>
@@ -2592,17 +2542,17 @@
       <c r="E48" s="19" t="n"/>
       <c r="F48" s="19" t="n"/>
       <c r="G48" s="19" t="n"/>
-      <c r="H48" s="122" t="n"/>
-      <c r="I48" s="32" t="n"/>
+      <c r="H48" s="95" t="n"/>
+      <c r="I48" s="31" t="n"/>
       <c r="J48" s="22" t="n"/>
       <c r="K48" s="21" t="n"/>
-      <c r="L48" s="33" t="n"/>
-      <c r="M48" s="123" t="n"/>
-      <c r="N48" s="122" t="n"/>
+      <c r="L48" s="32" t="n"/>
+      <c r="M48" s="96" t="n"/>
+      <c r="N48" s="95" t="n"/>
       <c r="O48" s="23" t="n"/>
       <c r="P48" s="24" t="n"/>
     </row>
-    <row r="49" ht="100.35" customFormat="1" customHeight="1" s="82">
+    <row r="49" ht="40.05" customFormat="1" customHeight="1" s="78">
       <c r="A49" s="18" t="n"/>
       <c r="B49" s="19" t="n"/>
       <c r="C49" s="19" t="n"/>
@@ -2610,919 +2560,919 @@
       <c r="E49" s="19" t="n"/>
       <c r="F49" s="19" t="n"/>
       <c r="G49" s="19" t="n"/>
-      <c r="H49" s="122" t="n"/>
-      <c r="I49" s="32" t="n"/>
+      <c r="H49" s="95" t="n"/>
+      <c r="I49" s="31" t="n"/>
       <c r="J49" s="22" t="n"/>
       <c r="K49" s="21" t="n"/>
-      <c r="L49" s="33" t="n"/>
-      <c r="M49" s="123" t="n"/>
-      <c r="N49" s="122" t="n"/>
+      <c r="L49" s="32" t="n"/>
+      <c r="M49" s="96" t="n"/>
+      <c r="N49" s="95" t="n"/>
       <c r="O49" s="23" t="n"/>
       <c r="P49" s="24" t="n"/>
     </row>
-    <row r="50" ht="128.25" customFormat="1" customHeight="1" s="82">
+    <row r="50" ht="128.25" customFormat="1" customHeight="1" s="78">
       <c r="A50" s="15" t="n"/>
-      <c r="B50" s="28" t="n"/>
-      <c r="C50" s="28" t="n"/>
-      <c r="D50" s="28" t="n"/>
-      <c r="E50" s="28" t="n"/>
-      <c r="F50" s="28" t="n"/>
-      <c r="G50" s="28" t="n"/>
-      <c r="H50" s="84" t="n"/>
+      <c r="B50" s="27" t="n"/>
+      <c r="C50" s="27" t="n"/>
+      <c r="D50" s="27" t="n"/>
+      <c r="E50" s="27" t="n"/>
+      <c r="F50" s="27" t="n"/>
+      <c r="G50" s="27" t="n"/>
+      <c r="H50" s="85" t="n"/>
       <c r="I50" s="15" t="n"/>
-      <c r="J50" s="30" t="n"/>
+      <c r="J50" s="29" t="n"/>
       <c r="K50" s="15" t="n"/>
-      <c r="M50" s="85" t="n"/>
+      <c r="M50" s="86" t="n"/>
       <c r="N50" s="15" t="n"/>
-      <c r="O50" s="31" t="n"/>
-    </row>
-    <row r="51" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O50" s="30" t="n"/>
+    </row>
+    <row r="51" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A51" s="15" t="n"/>
-      <c r="B51" s="28" t="n"/>
-      <c r="C51" s="28" t="n"/>
-      <c r="D51" s="28" t="n"/>
-      <c r="E51" s="28" t="n"/>
-      <c r="F51" s="28" t="n"/>
-      <c r="G51" s="28" t="n"/>
-      <c r="H51" s="84" t="n"/>
+      <c r="B51" s="27" t="n"/>
+      <c r="C51" s="27" t="n"/>
+      <c r="D51" s="27" t="n"/>
+      <c r="E51" s="27" t="n"/>
+      <c r="F51" s="27" t="n"/>
+      <c r="G51" s="27" t="n"/>
+      <c r="H51" s="85" t="n"/>
       <c r="I51" s="15" t="n"/>
-      <c r="J51" s="30" t="n"/>
+      <c r="J51" s="29" t="n"/>
       <c r="K51" s="15" t="n"/>
-      <c r="M51" s="85" t="n"/>
+      <c r="M51" s="86" t="n"/>
       <c r="N51" s="15" t="n"/>
-      <c r="O51" s="31" t="n"/>
-    </row>
-    <row r="52" ht="107.7" customFormat="1" customHeight="1" s="82">
+      <c r="O51" s="30" t="n"/>
+    </row>
+    <row r="52" ht="107.7" customFormat="1" customHeight="1" s="78">
       <c r="A52" s="15" t="n"/>
-      <c r="B52" s="28" t="n"/>
-      <c r="C52" s="28" t="n"/>
-      <c r="D52" s="28" t="n"/>
-      <c r="E52" s="28" t="n"/>
-      <c r="F52" s="28" t="n"/>
-      <c r="G52" s="28" t="n"/>
-      <c r="H52" s="84" t="n"/>
+      <c r="B52" s="27" t="n"/>
+      <c r="C52" s="27" t="n"/>
+      <c r="D52" s="27" t="n"/>
+      <c r="E52" s="27" t="n"/>
+      <c r="F52" s="27" t="n"/>
+      <c r="G52" s="27" t="n"/>
+      <c r="H52" s="85" t="n"/>
       <c r="I52" s="15" t="n"/>
-      <c r="J52" s="30" t="n"/>
+      <c r="J52" s="29" t="n"/>
       <c r="K52" s="15" t="n"/>
-      <c r="M52" s="85" t="n"/>
+      <c r="M52" s="86" t="n"/>
       <c r="N52" s="15" t="n"/>
-      <c r="O52" s="31" t="n"/>
-    </row>
-    <row r="53" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O52" s="30" t="n"/>
+    </row>
+    <row r="53" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A53" s="15" t="n"/>
-      <c r="B53" s="28" t="n"/>
-      <c r="C53" s="28" t="n"/>
-      <c r="D53" s="28" t="n"/>
-      <c r="E53" s="28" t="n"/>
-      <c r="F53" s="28" t="n"/>
-      <c r="G53" s="28" t="n"/>
-      <c r="H53" s="84" t="n"/>
+      <c r="B53" s="27" t="n"/>
+      <c r="C53" s="27" t="n"/>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="27" t="n"/>
+      <c r="F53" s="27" t="n"/>
+      <c r="G53" s="27" t="n"/>
+      <c r="H53" s="85" t="n"/>
       <c r="I53" s="15" t="n"/>
-      <c r="J53" s="30" t="n"/>
+      <c r="J53" s="29" t="n"/>
       <c r="K53" s="15" t="n"/>
-      <c r="M53" s="85" t="n"/>
+      <c r="M53" s="86" t="n"/>
       <c r="N53" s="15" t="n"/>
-      <c r="O53" s="31" t="n"/>
-    </row>
-    <row r="54" ht="114" customFormat="1" customHeight="1" s="82">
+      <c r="O53" s="30" t="n"/>
+    </row>
+    <row r="54" ht="114" customFormat="1" customHeight="1" s="78">
       <c r="A54" s="15" t="n"/>
-      <c r="B54" s="28" t="n"/>
-      <c r="C54" s="28" t="n"/>
-      <c r="D54" s="28" t="n"/>
-      <c r="E54" s="28" t="n"/>
-      <c r="F54" s="28" t="n"/>
-      <c r="G54" s="28" t="n"/>
-      <c r="H54" s="84" t="n"/>
+      <c r="B54" s="27" t="n"/>
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="n"/>
+      <c r="F54" s="27" t="n"/>
+      <c r="G54" s="27" t="n"/>
+      <c r="H54" s="85" t="n"/>
       <c r="I54" s="15" t="n"/>
       <c r="K54" s="15" t="n"/>
-      <c r="M54" s="85" t="n"/>
+      <c r="M54" s="86" t="n"/>
       <c r="N54" s="15" t="n"/>
-      <c r="O54" s="31" t="n"/>
-    </row>
-    <row r="55" ht="77.25" customFormat="1" customHeight="1" s="82">
+      <c r="O54" s="30" t="n"/>
+    </row>
+    <row r="55" ht="77.25" customFormat="1" customHeight="1" s="78">
       <c r="A55" s="15" t="n"/>
-      <c r="B55" s="28" t="n"/>
-      <c r="C55" s="28" t="n"/>
-      <c r="D55" s="28" t="n"/>
-      <c r="E55" s="28" t="n"/>
-      <c r="F55" s="28" t="n"/>
-      <c r="G55" s="28" t="n"/>
-      <c r="H55" s="84" t="n"/>
+      <c r="B55" s="27" t="n"/>
+      <c r="C55" s="27" t="n"/>
+      <c r="D55" s="27" t="n"/>
+      <c r="E55" s="27" t="n"/>
+      <c r="F55" s="27" t="n"/>
+      <c r="G55" s="27" t="n"/>
+      <c r="H55" s="85" t="n"/>
       <c r="I55" s="15" t="n"/>
       <c r="K55" s="15" t="n"/>
-      <c r="M55" s="85" t="n"/>
+      <c r="M55" s="86" t="n"/>
       <c r="N55" s="15" t="n"/>
-      <c r="O55" s="31" t="n"/>
-    </row>
-    <row r="56" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O55" s="30" t="n"/>
+    </row>
+    <row r="56" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A56" s="15" t="n"/>
-      <c r="B56" s="28" t="n"/>
-      <c r="C56" s="28" t="n"/>
-      <c r="D56" s="28" t="n"/>
-      <c r="E56" s="28" t="n"/>
-      <c r="F56" s="28" t="n"/>
-      <c r="G56" s="28" t="n"/>
-      <c r="H56" s="84" t="n"/>
+      <c r="B56" s="27" t="n"/>
+      <c r="C56" s="27" t="n"/>
+      <c r="D56" s="27" t="n"/>
+      <c r="E56" s="27" t="n"/>
+      <c r="F56" s="27" t="n"/>
+      <c r="G56" s="27" t="n"/>
+      <c r="H56" s="85" t="n"/>
       <c r="I56" s="15" t="n"/>
       <c r="K56" s="15" t="n"/>
-      <c r="M56" s="85" t="n"/>
+      <c r="M56" s="86" t="n"/>
       <c r="N56" s="15" t="n"/>
-      <c r="O56" s="31" t="n"/>
-    </row>
-    <row r="57" ht="72" customFormat="1" customHeight="1" s="82">
+      <c r="O56" s="30" t="n"/>
+    </row>
+    <row r="57" ht="72" customFormat="1" customHeight="1" s="78">
       <c r="A57" s="15" t="n"/>
-      <c r="B57" s="28" t="n"/>
-      <c r="C57" s="28" t="n"/>
-      <c r="D57" s="28" t="n"/>
-      <c r="E57" s="28" t="n"/>
-      <c r="F57" s="28" t="n"/>
-      <c r="G57" s="28" t="n"/>
-      <c r="H57" s="84" t="n"/>
+      <c r="B57" s="27" t="n"/>
+      <c r="C57" s="27" t="n"/>
+      <c r="D57" s="27" t="n"/>
+      <c r="E57" s="27" t="n"/>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="27" t="n"/>
+      <c r="H57" s="85" t="n"/>
       <c r="I57" s="15" t="n"/>
       <c r="K57" s="15" t="n"/>
-      <c r="M57" s="85" t="n"/>
+      <c r="M57" s="86" t="n"/>
       <c r="N57" s="15" t="n"/>
-      <c r="O57" s="31" t="n"/>
-    </row>
-    <row r="58" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O57" s="30" t="n"/>
+    </row>
+    <row r="58" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A58" s="15" t="n"/>
-      <c r="B58" s="28" t="n"/>
-      <c r="C58" s="28" t="n"/>
-      <c r="D58" s="28" t="n"/>
-      <c r="E58" s="28" t="n"/>
-      <c r="F58" s="28" t="n"/>
-      <c r="G58" s="28" t="n"/>
-      <c r="H58" s="84" t="n"/>
+      <c r="B58" s="27" t="n"/>
+      <c r="C58" s="27" t="n"/>
+      <c r="D58" s="27" t="n"/>
+      <c r="E58" s="27" t="n"/>
+      <c r="F58" s="27" t="n"/>
+      <c r="G58" s="27" t="n"/>
+      <c r="H58" s="85" t="n"/>
       <c r="I58" s="15" t="n"/>
       <c r="K58" s="15" t="n"/>
-      <c r="M58" s="85" t="n"/>
+      <c r="M58" s="86" t="n"/>
       <c r="N58" s="15" t="n"/>
-      <c r="O58" s="31" t="n"/>
-    </row>
-    <row r="59" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O58" s="30" t="n"/>
+    </row>
+    <row r="59" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A59" s="15" t="n"/>
-      <c r="B59" s="28" t="n"/>
-      <c r="C59" s="28" t="n"/>
-      <c r="D59" s="28" t="n"/>
-      <c r="E59" s="28" t="n"/>
-      <c r="F59" s="28" t="n"/>
-      <c r="G59" s="28" t="n"/>
-      <c r="H59" s="84" t="n"/>
+      <c r="B59" s="27" t="n"/>
+      <c r="C59" s="27" t="n"/>
+      <c r="D59" s="27" t="n"/>
+      <c r="E59" s="27" t="n"/>
+      <c r="F59" s="27" t="n"/>
+      <c r="G59" s="27" t="n"/>
+      <c r="H59" s="85" t="n"/>
       <c r="I59" s="15" t="n"/>
       <c r="K59" s="15" t="n"/>
-      <c r="M59" s="85" t="n"/>
+      <c r="M59" s="86" t="n"/>
       <c r="N59" s="15" t="n"/>
-      <c r="O59" s="31" t="n"/>
-    </row>
-    <row r="60" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O59" s="30" t="n"/>
+    </row>
+    <row r="60" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A60" s="15" t="n"/>
-      <c r="B60" s="28" t="n"/>
-      <c r="C60" s="28" t="n"/>
-      <c r="D60" s="28" t="n"/>
-      <c r="E60" s="28" t="n"/>
-      <c r="F60" s="28" t="n"/>
-      <c r="G60" s="28" t="n"/>
-      <c r="H60" s="84" t="n"/>
+      <c r="B60" s="27" t="n"/>
+      <c r="C60" s="27" t="n"/>
+      <c r="D60" s="27" t="n"/>
+      <c r="E60" s="27" t="n"/>
+      <c r="F60" s="27" t="n"/>
+      <c r="G60" s="27" t="n"/>
+      <c r="H60" s="85" t="n"/>
       <c r="I60" s="15" t="n"/>
       <c r="K60" s="15" t="n"/>
-      <c r="M60" s="85" t="n"/>
+      <c r="M60" s="86" t="n"/>
       <c r="N60" s="15" t="n"/>
-      <c r="O60" s="31" t="n"/>
-    </row>
-    <row r="61" ht="160.5" customFormat="1" customHeight="1" s="82">
+      <c r="O60" s="30" t="n"/>
+    </row>
+    <row r="61" ht="160.5" customFormat="1" customHeight="1" s="78">
       <c r="A61" s="15" t="n"/>
-      <c r="B61" s="28" t="n"/>
-      <c r="C61" s="28" t="n"/>
-      <c r="D61" s="28" t="n"/>
-      <c r="E61" s="28" t="n"/>
-      <c r="F61" s="28" t="n"/>
-      <c r="G61" s="28" t="n"/>
-      <c r="H61" s="84" t="n"/>
+      <c r="B61" s="27" t="n"/>
+      <c r="C61" s="27" t="n"/>
+      <c r="D61" s="27" t="n"/>
+      <c r="E61" s="27" t="n"/>
+      <c r="F61" s="27" t="n"/>
+      <c r="G61" s="27" t="n"/>
+      <c r="H61" s="85" t="n"/>
       <c r="I61" s="15" t="n"/>
       <c r="K61" s="15" t="n"/>
-      <c r="M61" s="85" t="n"/>
+      <c r="M61" s="86" t="n"/>
       <c r="N61" s="15" t="n"/>
-      <c r="O61" s="31" t="n"/>
-    </row>
-    <row r="62" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O61" s="30" t="n"/>
+    </row>
+    <row r="62" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A62" s="15" t="n"/>
-      <c r="B62" s="28" t="n"/>
-      <c r="C62" s="28" t="n"/>
-      <c r="D62" s="28" t="n"/>
-      <c r="E62" s="28" t="n"/>
-      <c r="F62" s="28" t="n"/>
-      <c r="G62" s="28" t="n"/>
-      <c r="H62" s="84" t="n"/>
+      <c r="B62" s="27" t="n"/>
+      <c r="C62" s="27" t="n"/>
+      <c r="D62" s="27" t="n"/>
+      <c r="E62" s="27" t="n"/>
+      <c r="F62" s="27" t="n"/>
+      <c r="G62" s="27" t="n"/>
+      <c r="H62" s="85" t="n"/>
       <c r="I62" s="15" t="n"/>
       <c r="K62" s="15" t="n"/>
-      <c r="M62" s="85" t="n"/>
+      <c r="M62" s="86" t="n"/>
       <c r="N62" s="15" t="n"/>
-      <c r="O62" s="31" t="n"/>
-    </row>
-    <row r="63" ht="73.34999999999999" customFormat="1" customHeight="1" s="82">
+      <c r="O62" s="30" t="n"/>
+    </row>
+    <row r="63" ht="73.34999999999999" customFormat="1" customHeight="1" s="78">
       <c r="A63" s="15" t="n"/>
-      <c r="B63" s="28" t="n"/>
-      <c r="C63" s="28" t="n"/>
-      <c r="D63" s="28" t="n"/>
-      <c r="E63" s="28" t="n"/>
-      <c r="F63" s="28" t="n"/>
-      <c r="G63" s="28" t="n"/>
-      <c r="H63" s="84" t="n"/>
+      <c r="B63" s="27" t="n"/>
+      <c r="C63" s="27" t="n"/>
+      <c r="D63" s="27" t="n"/>
+      <c r="E63" s="27" t="n"/>
+      <c r="F63" s="27" t="n"/>
+      <c r="G63" s="27" t="n"/>
+      <c r="H63" s="85" t="n"/>
       <c r="I63" s="15" t="n"/>
       <c r="K63" s="15" t="n"/>
-      <c r="M63" s="85" t="n"/>
+      <c r="M63" s="86" t="n"/>
       <c r="N63" s="15" t="n"/>
-      <c r="O63" s="31" t="n"/>
-    </row>
-    <row r="64" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O63" s="30" t="n"/>
+    </row>
+    <row r="64" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A64" s="15" t="n"/>
-      <c r="B64" s="28" t="n"/>
-      <c r="C64" s="28" t="n"/>
-      <c r="D64" s="28" t="n"/>
-      <c r="E64" s="28" t="n"/>
-      <c r="F64" s="28" t="n"/>
-      <c r="G64" s="28" t="n"/>
-      <c r="H64" s="84" t="n"/>
+      <c r="B64" s="27" t="n"/>
+      <c r="C64" s="27" t="n"/>
+      <c r="D64" s="27" t="n"/>
+      <c r="E64" s="27" t="n"/>
+      <c r="F64" s="27" t="n"/>
+      <c r="G64" s="27" t="n"/>
+      <c r="H64" s="85" t="n"/>
       <c r="I64" s="15" t="n"/>
       <c r="K64" s="15" t="n"/>
-      <c r="M64" s="85" t="n"/>
+      <c r="M64" s="86" t="n"/>
       <c r="N64" s="15" t="n"/>
-      <c r="O64" s="31" t="n"/>
-    </row>
-    <row r="65" ht="66" customFormat="1" customHeight="1" s="82">
+      <c r="O64" s="30" t="n"/>
+    </row>
+    <row r="65" ht="66" customFormat="1" customHeight="1" s="78">
       <c r="A65" s="15" t="n"/>
-      <c r="B65" s="28" t="n"/>
-      <c r="C65" s="28" t="n"/>
-      <c r="D65" s="28" t="n"/>
-      <c r="E65" s="28" t="n"/>
-      <c r="F65" s="28" t="n"/>
-      <c r="G65" s="28" t="n"/>
-      <c r="H65" s="84" t="n"/>
+      <c r="B65" s="27" t="n"/>
+      <c r="C65" s="27" t="n"/>
+      <c r="D65" s="27" t="n"/>
+      <c r="E65" s="27" t="n"/>
+      <c r="F65" s="27" t="n"/>
+      <c r="G65" s="27" t="n"/>
+      <c r="H65" s="85" t="n"/>
       <c r="I65" s="15" t="n"/>
       <c r="K65" s="15" t="n"/>
-      <c r="M65" s="85" t="n"/>
+      <c r="M65" s="86" t="n"/>
       <c r="N65" s="15" t="n"/>
-      <c r="O65" s="31" t="n"/>
-    </row>
-    <row r="66" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O65" s="30" t="n"/>
+    </row>
+    <row r="66" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A66" s="15" t="n"/>
-      <c r="B66" s="28" t="n"/>
-      <c r="C66" s="28" t="n"/>
-      <c r="D66" s="28" t="n"/>
-      <c r="E66" s="28" t="n"/>
-      <c r="F66" s="28" t="n"/>
-      <c r="G66" s="28" t="n"/>
-      <c r="H66" s="84" t="n"/>
+      <c r="B66" s="27" t="n"/>
+      <c r="C66" s="27" t="n"/>
+      <c r="D66" s="27" t="n"/>
+      <c r="E66" s="27" t="n"/>
+      <c r="F66" s="27" t="n"/>
+      <c r="G66" s="27" t="n"/>
+      <c r="H66" s="85" t="n"/>
       <c r="I66" s="15" t="n"/>
       <c r="K66" s="15" t="n"/>
-      <c r="M66" s="85" t="n"/>
+      <c r="M66" s="86" t="n"/>
       <c r="N66" s="15" t="n"/>
-      <c r="O66" s="31" t="n"/>
-    </row>
-    <row r="67" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O66" s="30" t="n"/>
+    </row>
+    <row r="67" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A67" s="15" t="n"/>
-      <c r="B67" s="28" t="n"/>
-      <c r="C67" s="28" t="n"/>
-      <c r="D67" s="28" t="n"/>
-      <c r="E67" s="28" t="n"/>
-      <c r="F67" s="28" t="n"/>
-      <c r="G67" s="28" t="n"/>
-      <c r="H67" s="84" t="n"/>
+      <c r="B67" s="27" t="n"/>
+      <c r="C67" s="27" t="n"/>
+      <c r="D67" s="27" t="n"/>
+      <c r="E67" s="27" t="n"/>
+      <c r="F67" s="27" t="n"/>
+      <c r="G67" s="27" t="n"/>
+      <c r="H67" s="85" t="n"/>
       <c r="I67" s="15" t="n"/>
       <c r="K67" s="15" t="n"/>
-      <c r="M67" s="85" t="n"/>
+      <c r="M67" s="86" t="n"/>
       <c r="N67" s="15" t="n"/>
-      <c r="O67" s="31" t="n"/>
-    </row>
-    <row r="68" ht="102" customFormat="1" customHeight="1" s="82">
+      <c r="O67" s="30" t="n"/>
+    </row>
+    <row r="68" ht="102" customFormat="1" customHeight="1" s="78">
       <c r="A68" s="15" t="n"/>
-      <c r="B68" s="28" t="n"/>
-      <c r="C68" s="28" t="n"/>
-      <c r="D68" s="28" t="n"/>
-      <c r="E68" s="28" t="n"/>
-      <c r="F68" s="28" t="n"/>
-      <c r="G68" s="28" t="n"/>
-      <c r="H68" s="84" t="n"/>
+      <c r="B68" s="27" t="n"/>
+      <c r="C68" s="27" t="n"/>
+      <c r="D68" s="27" t="n"/>
+      <c r="E68" s="27" t="n"/>
+      <c r="F68" s="27" t="n"/>
+      <c r="G68" s="27" t="n"/>
+      <c r="H68" s="85" t="n"/>
       <c r="I68" s="15" t="n"/>
       <c r="K68" s="15" t="n"/>
-      <c r="M68" s="85" t="n"/>
+      <c r="M68" s="86" t="n"/>
       <c r="N68" s="15" t="n"/>
-      <c r="O68" s="31" t="n"/>
-    </row>
-    <row r="69" ht="87.75" customFormat="1" customHeight="1" s="82">
+      <c r="O68" s="30" t="n"/>
+    </row>
+    <row r="69" ht="87.75" customFormat="1" customHeight="1" s="78">
       <c r="A69" s="15" t="n"/>
-      <c r="B69" s="28" t="n"/>
-      <c r="C69" s="28" t="n"/>
-      <c r="D69" s="28" t="n"/>
-      <c r="E69" s="28" t="n"/>
-      <c r="F69" s="28" t="n"/>
-      <c r="G69" s="28" t="n"/>
-      <c r="H69" s="84" t="n"/>
+      <c r="B69" s="27" t="n"/>
+      <c r="C69" s="27" t="n"/>
+      <c r="D69" s="27" t="n"/>
+      <c r="E69" s="27" t="n"/>
+      <c r="F69" s="27" t="n"/>
+      <c r="G69" s="27" t="n"/>
+      <c r="H69" s="85" t="n"/>
       <c r="I69" s="15" t="n"/>
       <c r="K69" s="15" t="n"/>
-      <c r="M69" s="85" t="n"/>
+      <c r="M69" s="86" t="n"/>
       <c r="N69" s="15" t="n"/>
-      <c r="O69" s="31" t="n"/>
-    </row>
-    <row r="70" ht="120.6" customFormat="1" customHeight="1" s="82">
+      <c r="O69" s="30" t="n"/>
+    </row>
+    <row r="70" ht="120.6" customFormat="1" customHeight="1" s="78">
       <c r="A70" s="15" t="n"/>
-      <c r="B70" s="28" t="n"/>
-      <c r="C70" s="28" t="n"/>
-      <c r="D70" s="28" t="n"/>
-      <c r="E70" s="28" t="n"/>
-      <c r="F70" s="28" t="n"/>
-      <c r="G70" s="28" t="n"/>
-      <c r="H70" s="84" t="n"/>
+      <c r="B70" s="27" t="n"/>
+      <c r="C70" s="27" t="n"/>
+      <c r="D70" s="27" t="n"/>
+      <c r="E70" s="27" t="n"/>
+      <c r="F70" s="27" t="n"/>
+      <c r="G70" s="27" t="n"/>
+      <c r="H70" s="85" t="n"/>
       <c r="I70" s="15" t="n"/>
       <c r="K70" s="15" t="n"/>
-      <c r="M70" s="85" t="n"/>
+      <c r="M70" s="86" t="n"/>
       <c r="N70" s="15" t="n"/>
-      <c r="O70" s="31" t="n"/>
-    </row>
-    <row r="71" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O70" s="30" t="n"/>
+    </row>
+    <row r="71" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A71" s="15" t="n"/>
-      <c r="B71" s="28" t="n"/>
-      <c r="C71" s="28" t="n"/>
-      <c r="D71" s="28" t="n"/>
-      <c r="E71" s="28" t="n"/>
-      <c r="F71" s="28" t="n"/>
-      <c r="G71" s="28" t="n"/>
-      <c r="H71" s="84" t="n"/>
+      <c r="B71" s="27" t="n"/>
+      <c r="C71" s="27" t="n"/>
+      <c r="D71" s="27" t="n"/>
+      <c r="E71" s="27" t="n"/>
+      <c r="F71" s="27" t="n"/>
+      <c r="G71" s="27" t="n"/>
+      <c r="H71" s="85" t="n"/>
       <c r="I71" s="15" t="n"/>
       <c r="K71" s="15" t="n"/>
-      <c r="M71" s="85" t="n"/>
+      <c r="M71" s="86" t="n"/>
       <c r="N71" s="15" t="n"/>
-      <c r="O71" s="31" t="n"/>
-    </row>
-    <row r="72" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O71" s="30" t="n"/>
+    </row>
+    <row r="72" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A72" s="15" t="n"/>
-      <c r="B72" s="28" t="n"/>
-      <c r="C72" s="28" t="n"/>
-      <c r="D72" s="28" t="n"/>
-      <c r="E72" s="28" t="n"/>
-      <c r="F72" s="28" t="n"/>
-      <c r="G72" s="28" t="n"/>
-      <c r="H72" s="84" t="n"/>
+      <c r="B72" s="27" t="n"/>
+      <c r="C72" s="27" t="n"/>
+      <c r="D72" s="27" t="n"/>
+      <c r="E72" s="27" t="n"/>
+      <c r="F72" s="27" t="n"/>
+      <c r="G72" s="27" t="n"/>
+      <c r="H72" s="85" t="n"/>
       <c r="I72" s="15" t="n"/>
       <c r="K72" s="15" t="n"/>
-      <c r="M72" s="85" t="n"/>
+      <c r="M72" s="86" t="n"/>
       <c r="N72" s="15" t="n"/>
-      <c r="O72" s="31" t="n"/>
-    </row>
-    <row r="73" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O72" s="30" t="n"/>
+    </row>
+    <row r="73" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A73" s="15" t="n"/>
-      <c r="B73" s="28" t="n"/>
-      <c r="C73" s="28" t="n"/>
-      <c r="D73" s="28" t="n"/>
-      <c r="E73" s="28" t="n"/>
-      <c r="F73" s="28" t="n"/>
-      <c r="G73" s="28" t="n"/>
-      <c r="H73" s="84" t="n"/>
+      <c r="B73" s="27" t="n"/>
+      <c r="C73" s="27" t="n"/>
+      <c r="D73" s="27" t="n"/>
+      <c r="E73" s="27" t="n"/>
+      <c r="F73" s="27" t="n"/>
+      <c r="G73" s="27" t="n"/>
+      <c r="H73" s="85" t="n"/>
       <c r="I73" s="15" t="n"/>
       <c r="K73" s="15" t="n"/>
-      <c r="M73" s="85" t="n"/>
+      <c r="M73" s="86" t="n"/>
       <c r="N73" s="15" t="n"/>
-      <c r="O73" s="31" t="n"/>
-    </row>
-    <row r="74" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O73" s="30" t="n"/>
+    </row>
+    <row r="74" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A74" s="15" t="n"/>
-      <c r="B74" s="28" t="n"/>
-      <c r="C74" s="28" t="n"/>
-      <c r="D74" s="28" t="n"/>
-      <c r="E74" s="28" t="n"/>
-      <c r="F74" s="28" t="n"/>
-      <c r="G74" s="28" t="n"/>
-      <c r="H74" s="84" t="n"/>
+      <c r="B74" s="27" t="n"/>
+      <c r="C74" s="27" t="n"/>
+      <c r="D74" s="27" t="n"/>
+      <c r="E74" s="27" t="n"/>
+      <c r="F74" s="27" t="n"/>
+      <c r="G74" s="27" t="n"/>
+      <c r="H74" s="85" t="n"/>
       <c r="I74" s="15" t="n"/>
       <c r="K74" s="15" t="n"/>
-      <c r="M74" s="85" t="n"/>
+      <c r="M74" s="86" t="n"/>
       <c r="N74" s="15" t="n"/>
-      <c r="O74" s="31" t="n"/>
-    </row>
-    <row r="75" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O74" s="30" t="n"/>
+    </row>
+    <row r="75" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A75" s="15" t="n"/>
-      <c r="B75" s="28" t="n"/>
-      <c r="C75" s="28" t="n"/>
-      <c r="D75" s="28" t="n"/>
-      <c r="E75" s="28" t="n"/>
-      <c r="F75" s="28" t="n"/>
-      <c r="G75" s="28" t="n"/>
-      <c r="H75" s="84" t="n"/>
+      <c r="B75" s="27" t="n"/>
+      <c r="C75" s="27" t="n"/>
+      <c r="D75" s="27" t="n"/>
+      <c r="E75" s="27" t="n"/>
+      <c r="F75" s="27" t="n"/>
+      <c r="G75" s="27" t="n"/>
+      <c r="H75" s="85" t="n"/>
       <c r="I75" s="15" t="n"/>
       <c r="K75" s="15" t="n"/>
-      <c r="M75" s="85" t="n"/>
+      <c r="M75" s="86" t="n"/>
       <c r="N75" s="15" t="n"/>
-      <c r="O75" s="31" t="n"/>
-    </row>
-    <row r="76" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O75" s="30" t="n"/>
+    </row>
+    <row r="76" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A76" s="15" t="n"/>
-      <c r="B76" s="28" t="n"/>
-      <c r="C76" s="28" t="n"/>
-      <c r="D76" s="28" t="n"/>
-      <c r="E76" s="28" t="n"/>
-      <c r="F76" s="28" t="n"/>
-      <c r="G76" s="28" t="n"/>
-      <c r="H76" s="84" t="n"/>
+      <c r="B76" s="27" t="n"/>
+      <c r="C76" s="27" t="n"/>
+      <c r="D76" s="27" t="n"/>
+      <c r="E76" s="27" t="n"/>
+      <c r="F76" s="27" t="n"/>
+      <c r="G76" s="27" t="n"/>
+      <c r="H76" s="85" t="n"/>
       <c r="I76" s="15" t="n"/>
       <c r="K76" s="15" t="n"/>
-      <c r="M76" s="85" t="n"/>
+      <c r="M76" s="86" t="n"/>
       <c r="N76" s="15" t="n"/>
-      <c r="O76" s="31" t="n"/>
-    </row>
-    <row r="77" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O76" s="30" t="n"/>
+    </row>
+    <row r="77" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A77" s="15" t="n"/>
-      <c r="B77" s="28" t="n"/>
-      <c r="C77" s="28" t="n"/>
-      <c r="D77" s="28" t="n"/>
-      <c r="E77" s="28" t="n"/>
-      <c r="F77" s="28" t="n"/>
-      <c r="G77" s="28" t="n"/>
-      <c r="H77" s="84" t="n"/>
+      <c r="B77" s="27" t="n"/>
+      <c r="C77" s="27" t="n"/>
+      <c r="D77" s="27" t="n"/>
+      <c r="E77" s="27" t="n"/>
+      <c r="F77" s="27" t="n"/>
+      <c r="G77" s="27" t="n"/>
+      <c r="H77" s="85" t="n"/>
       <c r="I77" s="15" t="n"/>
       <c r="K77" s="15" t="n"/>
-      <c r="M77" s="85" t="n"/>
+      <c r="M77" s="86" t="n"/>
       <c r="N77" s="15" t="n"/>
-      <c r="O77" s="31" t="n"/>
-    </row>
-    <row r="78" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O77" s="30" t="n"/>
+    </row>
+    <row r="78" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A78" s="15" t="n"/>
-      <c r="B78" s="28" t="n"/>
-      <c r="C78" s="28" t="n"/>
-      <c r="D78" s="28" t="n"/>
-      <c r="E78" s="28" t="n"/>
-      <c r="F78" s="28" t="n"/>
-      <c r="G78" s="28" t="n"/>
-      <c r="H78" s="84" t="n"/>
+      <c r="B78" s="27" t="n"/>
+      <c r="C78" s="27" t="n"/>
+      <c r="D78" s="27" t="n"/>
+      <c r="E78" s="27" t="n"/>
+      <c r="F78" s="27" t="n"/>
+      <c r="G78" s="27" t="n"/>
+      <c r="H78" s="85" t="n"/>
       <c r="I78" s="15" t="n"/>
       <c r="K78" s="15" t="n"/>
-      <c r="M78" s="85" t="n"/>
+      <c r="M78" s="86" t="n"/>
       <c r="N78" s="15" t="n"/>
-      <c r="O78" s="31" t="n"/>
-    </row>
-    <row r="79" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O78" s="30" t="n"/>
+    </row>
+    <row r="79" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A79" s="15" t="n"/>
-      <c r="B79" s="28" t="n"/>
-      <c r="C79" s="28" t="n"/>
-      <c r="D79" s="28" t="n"/>
-      <c r="E79" s="28" t="n"/>
-      <c r="F79" s="28" t="n"/>
-      <c r="G79" s="28" t="n"/>
-      <c r="H79" s="84" t="n"/>
+      <c r="B79" s="27" t="n"/>
+      <c r="C79" s="27" t="n"/>
+      <c r="D79" s="27" t="n"/>
+      <c r="E79" s="27" t="n"/>
+      <c r="F79" s="27" t="n"/>
+      <c r="G79" s="27" t="n"/>
+      <c r="H79" s="85" t="n"/>
       <c r="I79" s="15" t="n"/>
       <c r="K79" s="15" t="n"/>
-      <c r="M79" s="85" t="n"/>
+      <c r="M79" s="86" t="n"/>
       <c r="N79" s="15" t="n"/>
-      <c r="O79" s="31" t="n"/>
-    </row>
-    <row r="80" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O79" s="30" t="n"/>
+    </row>
+    <row r="80" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A80" s="15" t="n"/>
-      <c r="B80" s="28" t="n"/>
-      <c r="C80" s="28" t="n"/>
-      <c r="D80" s="28" t="n"/>
-      <c r="E80" s="28" t="n"/>
-      <c r="F80" s="28" t="n"/>
-      <c r="G80" s="28" t="n"/>
-      <c r="H80" s="84" t="n"/>
+      <c r="B80" s="27" t="n"/>
+      <c r="C80" s="27" t="n"/>
+      <c r="D80" s="27" t="n"/>
+      <c r="E80" s="27" t="n"/>
+      <c r="F80" s="27" t="n"/>
+      <c r="G80" s="27" t="n"/>
+      <c r="H80" s="85" t="n"/>
       <c r="I80" s="15" t="n"/>
       <c r="K80" s="15" t="n"/>
-      <c r="M80" s="85" t="n"/>
+      <c r="M80" s="86" t="n"/>
       <c r="N80" s="15" t="n"/>
-      <c r="O80" s="31" t="n"/>
-    </row>
-    <row r="81" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O80" s="30" t="n"/>
+    </row>
+    <row r="81" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A81" s="15" t="n"/>
-      <c r="B81" s="28" t="n"/>
-      <c r="C81" s="28" t="n"/>
-      <c r="D81" s="28" t="n"/>
-      <c r="E81" s="28" t="n"/>
-      <c r="F81" s="28" t="n"/>
-      <c r="G81" s="28" t="n"/>
-      <c r="H81" s="84" t="n"/>
+      <c r="B81" s="27" t="n"/>
+      <c r="C81" s="27" t="n"/>
+      <c r="D81" s="27" t="n"/>
+      <c r="E81" s="27" t="n"/>
+      <c r="F81" s="27" t="n"/>
+      <c r="G81" s="27" t="n"/>
+      <c r="H81" s="85" t="n"/>
       <c r="I81" s="15" t="n"/>
       <c r="K81" s="15" t="n"/>
-      <c r="M81" s="85" t="n"/>
+      <c r="M81" s="86" t="n"/>
       <c r="N81" s="15" t="n"/>
-      <c r="O81" s="31" t="n"/>
-    </row>
-    <row r="82" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O81" s="30" t="n"/>
+    </row>
+    <row r="82" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A82" s="15" t="n"/>
-      <c r="B82" s="28" t="n"/>
-      <c r="C82" s="28" t="n"/>
-      <c r="D82" s="28" t="n"/>
-      <c r="E82" s="28" t="n"/>
-      <c r="F82" s="28" t="n"/>
-      <c r="G82" s="28" t="n"/>
-      <c r="H82" s="84" t="n"/>
+      <c r="B82" s="27" t="n"/>
+      <c r="C82" s="27" t="n"/>
+      <c r="D82" s="27" t="n"/>
+      <c r="E82" s="27" t="n"/>
+      <c r="F82" s="27" t="n"/>
+      <c r="G82" s="27" t="n"/>
+      <c r="H82" s="85" t="n"/>
       <c r="I82" s="15" t="n"/>
       <c r="K82" s="15" t="n"/>
-      <c r="M82" s="85" t="n"/>
+      <c r="M82" s="86" t="n"/>
       <c r="N82" s="15" t="n"/>
-      <c r="O82" s="31" t="n"/>
-    </row>
-    <row r="83" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O82" s="30" t="n"/>
+    </row>
+    <row r="83" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A83" s="15" t="n"/>
-      <c r="B83" s="28" t="n"/>
-      <c r="C83" s="28" t="n"/>
-      <c r="D83" s="28" t="n"/>
-      <c r="E83" s="28" t="n"/>
-      <c r="F83" s="28" t="n"/>
-      <c r="G83" s="28" t="n"/>
-      <c r="H83" s="84" t="n"/>
+      <c r="B83" s="27" t="n"/>
+      <c r="C83" s="27" t="n"/>
+      <c r="D83" s="27" t="n"/>
+      <c r="E83" s="27" t="n"/>
+      <c r="F83" s="27" t="n"/>
+      <c r="G83" s="27" t="n"/>
+      <c r="H83" s="85" t="n"/>
       <c r="I83" s="15" t="n"/>
       <c r="K83" s="15" t="n"/>
-      <c r="M83" s="85" t="n"/>
+      <c r="M83" s="86" t="n"/>
       <c r="N83" s="15" t="n"/>
-      <c r="O83" s="31" t="n"/>
-    </row>
-    <row r="84" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O83" s="30" t="n"/>
+    </row>
+    <row r="84" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A84" s="15" t="n"/>
-      <c r="B84" s="28" t="n"/>
-      <c r="C84" s="28" t="n"/>
-      <c r="D84" s="28" t="n"/>
-      <c r="E84" s="28" t="n"/>
-      <c r="F84" s="28" t="n"/>
-      <c r="G84" s="28" t="n"/>
-      <c r="H84" s="84" t="n"/>
+      <c r="B84" s="27" t="n"/>
+      <c r="C84" s="27" t="n"/>
+      <c r="D84" s="27" t="n"/>
+      <c r="E84" s="27" t="n"/>
+      <c r="F84" s="27" t="n"/>
+      <c r="G84" s="27" t="n"/>
+      <c r="H84" s="85" t="n"/>
       <c r="I84" s="15" t="n"/>
       <c r="K84" s="15" t="n"/>
-      <c r="M84" s="85" t="n"/>
+      <c r="M84" s="86" t="n"/>
       <c r="N84" s="15" t="n"/>
-      <c r="O84" s="31" t="n"/>
-    </row>
-    <row r="85" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O84" s="30" t="n"/>
+    </row>
+    <row r="85" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A85" s="15" t="n"/>
-      <c r="B85" s="28" t="n"/>
-      <c r="C85" s="28" t="n"/>
-      <c r="D85" s="28" t="n"/>
-      <c r="E85" s="28" t="n"/>
-      <c r="F85" s="28" t="n"/>
-      <c r="G85" s="28" t="n"/>
-      <c r="H85" s="84" t="n"/>
+      <c r="B85" s="27" t="n"/>
+      <c r="C85" s="27" t="n"/>
+      <c r="D85" s="27" t="n"/>
+      <c r="E85" s="27" t="n"/>
+      <c r="F85" s="27" t="n"/>
+      <c r="G85" s="27" t="n"/>
+      <c r="H85" s="85" t="n"/>
       <c r="I85" s="15" t="n"/>
       <c r="K85" s="15" t="n"/>
-      <c r="M85" s="85" t="n"/>
+      <c r="M85" s="86" t="n"/>
       <c r="N85" s="15" t="n"/>
-      <c r="O85" s="31" t="n"/>
-    </row>
-    <row r="86" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O85" s="30" t="n"/>
+    </row>
+    <row r="86" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A86" s="15" t="n"/>
-      <c r="B86" s="28" t="n"/>
-      <c r="C86" s="28" t="n"/>
-      <c r="D86" s="28" t="n"/>
-      <c r="E86" s="28" t="n"/>
-      <c r="F86" s="28" t="n"/>
-      <c r="G86" s="28" t="n"/>
-      <c r="H86" s="84" t="n"/>
+      <c r="B86" s="27" t="n"/>
+      <c r="C86" s="27" t="n"/>
+      <c r="D86" s="27" t="n"/>
+      <c r="E86" s="27" t="n"/>
+      <c r="F86" s="27" t="n"/>
+      <c r="G86" s="27" t="n"/>
+      <c r="H86" s="85" t="n"/>
       <c r="I86" s="15" t="n"/>
       <c r="K86" s="15" t="n"/>
-      <c r="M86" s="85" t="n"/>
+      <c r="M86" s="86" t="n"/>
       <c r="N86" s="15" t="n"/>
-      <c r="O86" s="31" t="n"/>
-    </row>
-    <row r="87" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O86" s="30" t="n"/>
+    </row>
+    <row r="87" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A87" s="15" t="n"/>
-      <c r="B87" s="28" t="n"/>
-      <c r="C87" s="28" t="n"/>
-      <c r="D87" s="28" t="n"/>
-      <c r="E87" s="28" t="n"/>
-      <c r="F87" s="28" t="n"/>
-      <c r="G87" s="28" t="n"/>
-      <c r="H87" s="84" t="n"/>
+      <c r="B87" s="27" t="n"/>
+      <c r="C87" s="27" t="n"/>
+      <c r="D87" s="27" t="n"/>
+      <c r="E87" s="27" t="n"/>
+      <c r="F87" s="27" t="n"/>
+      <c r="G87" s="27" t="n"/>
+      <c r="H87" s="85" t="n"/>
       <c r="I87" s="15" t="n"/>
       <c r="K87" s="15" t="n"/>
-      <c r="M87" s="85" t="n"/>
+      <c r="M87" s="86" t="n"/>
       <c r="N87" s="15" t="n"/>
-      <c r="O87" s="31" t="n"/>
-    </row>
-    <row r="88" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O87" s="30" t="n"/>
+    </row>
+    <row r="88" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A88" s="15" t="n"/>
-      <c r="B88" s="28" t="n"/>
-      <c r="C88" s="28" t="n"/>
-      <c r="D88" s="28" t="n"/>
-      <c r="E88" s="28" t="n"/>
-      <c r="F88" s="28" t="n"/>
-      <c r="G88" s="28" t="n"/>
-      <c r="H88" s="84" t="n"/>
+      <c r="B88" s="27" t="n"/>
+      <c r="C88" s="27" t="n"/>
+      <c r="D88" s="27" t="n"/>
+      <c r="E88" s="27" t="n"/>
+      <c r="F88" s="27" t="n"/>
+      <c r="G88" s="27" t="n"/>
+      <c r="H88" s="85" t="n"/>
       <c r="I88" s="15" t="n"/>
       <c r="K88" s="15" t="n"/>
-      <c r="M88" s="85" t="n"/>
+      <c r="M88" s="86" t="n"/>
       <c r="N88" s="15" t="n"/>
-      <c r="O88" s="31" t="n"/>
-    </row>
-    <row r="89" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O88" s="30" t="n"/>
+    </row>
+    <row r="89" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A89" s="15" t="n"/>
-      <c r="B89" s="28" t="n"/>
-      <c r="C89" s="28" t="n"/>
-      <c r="D89" s="28" t="n"/>
-      <c r="E89" s="28" t="n"/>
-      <c r="F89" s="28" t="n"/>
-      <c r="G89" s="28" t="n"/>
-      <c r="H89" s="84" t="n"/>
+      <c r="B89" s="27" t="n"/>
+      <c r="C89" s="27" t="n"/>
+      <c r="D89" s="27" t="n"/>
+      <c r="E89" s="27" t="n"/>
+      <c r="F89" s="27" t="n"/>
+      <c r="G89" s="27" t="n"/>
+      <c r="H89" s="85" t="n"/>
       <c r="I89" s="15" t="n"/>
       <c r="K89" s="15" t="n"/>
-      <c r="M89" s="85" t="n"/>
+      <c r="M89" s="86" t="n"/>
       <c r="N89" s="15" t="n"/>
-      <c r="O89" s="31" t="n"/>
-    </row>
-    <row r="90" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O89" s="30" t="n"/>
+    </row>
+    <row r="90" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A90" s="15" t="n"/>
-      <c r="B90" s="28" t="n"/>
-      <c r="C90" s="28" t="n"/>
-      <c r="D90" s="28" t="n"/>
-      <c r="E90" s="28" t="n"/>
-      <c r="F90" s="28" t="n"/>
-      <c r="G90" s="28" t="n"/>
-      <c r="H90" s="84" t="n"/>
+      <c r="B90" s="27" t="n"/>
+      <c r="C90" s="27" t="n"/>
+      <c r="D90" s="27" t="n"/>
+      <c r="E90" s="27" t="n"/>
+      <c r="F90" s="27" t="n"/>
+      <c r="G90" s="27" t="n"/>
+      <c r="H90" s="85" t="n"/>
       <c r="I90" s="15" t="n"/>
       <c r="K90" s="15" t="n"/>
-      <c r="M90" s="85" t="n"/>
+      <c r="M90" s="86" t="n"/>
       <c r="N90" s="15" t="n"/>
-      <c r="O90" s="31" t="n"/>
-    </row>
-    <row r="91" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O90" s="30" t="n"/>
+    </row>
+    <row r="91" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A91" s="15" t="n"/>
-      <c r="B91" s="28" t="n"/>
-      <c r="C91" s="28" t="n"/>
-      <c r="D91" s="28" t="n"/>
-      <c r="E91" s="28" t="n"/>
-      <c r="F91" s="28" t="n"/>
-      <c r="G91" s="28" t="n"/>
-      <c r="H91" s="84" t="n"/>
+      <c r="B91" s="27" t="n"/>
+      <c r="C91" s="27" t="n"/>
+      <c r="D91" s="27" t="n"/>
+      <c r="E91" s="27" t="n"/>
+      <c r="F91" s="27" t="n"/>
+      <c r="G91" s="27" t="n"/>
+      <c r="H91" s="85" t="n"/>
       <c r="I91" s="15" t="n"/>
       <c r="K91" s="15" t="n"/>
-      <c r="M91" s="85" t="n"/>
+      <c r="M91" s="86" t="n"/>
       <c r="N91" s="15" t="n"/>
-      <c r="O91" s="31" t="n"/>
-    </row>
-    <row r="92" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O91" s="30" t="n"/>
+    </row>
+    <row r="92" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A92" s="15" t="n"/>
-      <c r="B92" s="28" t="n"/>
-      <c r="C92" s="28" t="n"/>
-      <c r="D92" s="28" t="n"/>
-      <c r="E92" s="28" t="n"/>
-      <c r="F92" s="28" t="n"/>
-      <c r="G92" s="28" t="n"/>
-      <c r="H92" s="84" t="n"/>
+      <c r="B92" s="27" t="n"/>
+      <c r="C92" s="27" t="n"/>
+      <c r="D92" s="27" t="n"/>
+      <c r="E92" s="27" t="n"/>
+      <c r="F92" s="27" t="n"/>
+      <c r="G92" s="27" t="n"/>
+      <c r="H92" s="85" t="n"/>
       <c r="I92" s="15" t="n"/>
       <c r="K92" s="15" t="n"/>
-      <c r="M92" s="85" t="n"/>
+      <c r="M92" s="86" t="n"/>
       <c r="N92" s="15" t="n"/>
-      <c r="O92" s="31" t="n"/>
-    </row>
-    <row r="93" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O92" s="30" t="n"/>
+    </row>
+    <row r="93" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A93" s="15" t="n"/>
-      <c r="B93" s="28" t="n"/>
-      <c r="C93" s="28" t="n"/>
-      <c r="D93" s="28" t="n"/>
-      <c r="E93" s="28" t="n"/>
-      <c r="F93" s="28" t="n"/>
-      <c r="G93" s="28" t="n"/>
-      <c r="H93" s="84" t="n"/>
+      <c r="B93" s="27" t="n"/>
+      <c r="C93" s="27" t="n"/>
+      <c r="D93" s="27" t="n"/>
+      <c r="E93" s="27" t="n"/>
+      <c r="F93" s="27" t="n"/>
+      <c r="G93" s="27" t="n"/>
+      <c r="H93" s="85" t="n"/>
       <c r="I93" s="15" t="n"/>
       <c r="K93" s="15" t="n"/>
-      <c r="M93" s="85" t="n"/>
+      <c r="M93" s="86" t="n"/>
       <c r="N93" s="15" t="n"/>
-      <c r="O93" s="31" t="n"/>
-    </row>
-    <row r="94" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O93" s="30" t="n"/>
+    </row>
+    <row r="94" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A94" s="15" t="n"/>
-      <c r="B94" s="28" t="n"/>
-      <c r="C94" s="28" t="n"/>
-      <c r="D94" s="28" t="n"/>
-      <c r="E94" s="28" t="n"/>
-      <c r="F94" s="28" t="n"/>
-      <c r="G94" s="28" t="n"/>
-      <c r="H94" s="84" t="n"/>
+      <c r="B94" s="27" t="n"/>
+      <c r="C94" s="27" t="n"/>
+      <c r="D94" s="27" t="n"/>
+      <c r="E94" s="27" t="n"/>
+      <c r="F94" s="27" t="n"/>
+      <c r="G94" s="27" t="n"/>
+      <c r="H94" s="85" t="n"/>
       <c r="I94" s="15" t="n"/>
       <c r="K94" s="15" t="n"/>
-      <c r="M94" s="85" t="n"/>
+      <c r="M94" s="86" t="n"/>
       <c r="N94" s="15" t="n"/>
-      <c r="O94" s="31" t="n"/>
-    </row>
-    <row r="95" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O94" s="30" t="n"/>
+    </row>
+    <row r="95" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A95" s="15" t="n"/>
-      <c r="B95" s="28" t="n"/>
-      <c r="C95" s="28" t="n"/>
-      <c r="D95" s="28" t="n"/>
-      <c r="E95" s="28" t="n"/>
-      <c r="F95" s="28" t="n"/>
-      <c r="G95" s="28" t="n"/>
-      <c r="H95" s="84" t="n"/>
+      <c r="B95" s="27" t="n"/>
+      <c r="C95" s="27" t="n"/>
+      <c r="D95" s="27" t="n"/>
+      <c r="E95" s="27" t="n"/>
+      <c r="F95" s="27" t="n"/>
+      <c r="G95" s="27" t="n"/>
+      <c r="H95" s="85" t="n"/>
       <c r="I95" s="15" t="n"/>
       <c r="K95" s="15" t="n"/>
-      <c r="M95" s="85" t="n"/>
+      <c r="M95" s="86" t="n"/>
       <c r="N95" s="15" t="n"/>
-      <c r="O95" s="31" t="n"/>
-    </row>
-    <row r="96" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O95" s="30" t="n"/>
+    </row>
+    <row r="96" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A96" s="15" t="n"/>
-      <c r="B96" s="28" t="n"/>
-      <c r="C96" s="28" t="n"/>
-      <c r="D96" s="28" t="n"/>
-      <c r="E96" s="28" t="n"/>
-      <c r="F96" s="28" t="n"/>
-      <c r="G96" s="28" t="n"/>
-      <c r="H96" s="84" t="n"/>
+      <c r="B96" s="27" t="n"/>
+      <c r="C96" s="27" t="n"/>
+      <c r="D96" s="27" t="n"/>
+      <c r="E96" s="27" t="n"/>
+      <c r="F96" s="27" t="n"/>
+      <c r="G96" s="27" t="n"/>
+      <c r="H96" s="85" t="n"/>
       <c r="I96" s="15" t="n"/>
       <c r="K96" s="15" t="n"/>
-      <c r="M96" s="85" t="n"/>
+      <c r="M96" s="86" t="n"/>
       <c r="N96" s="15" t="n"/>
-      <c r="O96" s="31" t="n"/>
-    </row>
-    <row r="97" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O96" s="30" t="n"/>
+    </row>
+    <row r="97" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A97" s="15" t="n"/>
-      <c r="B97" s="28" t="n"/>
-      <c r="C97" s="28" t="n"/>
-      <c r="D97" s="28" t="n"/>
-      <c r="E97" s="28" t="n"/>
-      <c r="F97" s="28" t="n"/>
-      <c r="G97" s="28" t="n"/>
-      <c r="H97" s="84" t="n"/>
+      <c r="B97" s="27" t="n"/>
+      <c r="C97" s="27" t="n"/>
+      <c r="D97" s="27" t="n"/>
+      <c r="E97" s="27" t="n"/>
+      <c r="F97" s="27" t="n"/>
+      <c r="G97" s="27" t="n"/>
+      <c r="H97" s="85" t="n"/>
       <c r="I97" s="15" t="n"/>
       <c r="K97" s="15" t="n"/>
-      <c r="M97" s="85" t="n"/>
+      <c r="M97" s="86" t="n"/>
       <c r="N97" s="15" t="n"/>
-      <c r="O97" s="31" t="n"/>
-    </row>
-    <row r="98" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O97" s="30" t="n"/>
+    </row>
+    <row r="98" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A98" s="15" t="n"/>
-      <c r="B98" s="28" t="n"/>
-      <c r="C98" s="28" t="n"/>
-      <c r="D98" s="28" t="n"/>
-      <c r="E98" s="28" t="n"/>
-      <c r="F98" s="28" t="n"/>
-      <c r="G98" s="28" t="n"/>
-      <c r="H98" s="84" t="n"/>
+      <c r="B98" s="27" t="n"/>
+      <c r="C98" s="27" t="n"/>
+      <c r="D98" s="27" t="n"/>
+      <c r="E98" s="27" t="n"/>
+      <c r="F98" s="27" t="n"/>
+      <c r="G98" s="27" t="n"/>
+      <c r="H98" s="85" t="n"/>
       <c r="I98" s="15" t="n"/>
       <c r="K98" s="15" t="n"/>
-      <c r="M98" s="85" t="n"/>
+      <c r="M98" s="86" t="n"/>
       <c r="N98" s="15" t="n"/>
-      <c r="O98" s="31" t="n"/>
-    </row>
-    <row r="99" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O98" s="30" t="n"/>
+    </row>
+    <row r="99" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A99" s="15" t="n"/>
-      <c r="B99" s="28" t="n"/>
-      <c r="C99" s="28" t="n"/>
-      <c r="D99" s="28" t="n"/>
-      <c r="E99" s="28" t="n"/>
-      <c r="F99" s="28" t="n"/>
-      <c r="G99" s="28" t="n"/>
-      <c r="H99" s="84" t="n"/>
+      <c r="B99" s="27" t="n"/>
+      <c r="C99" s="27" t="n"/>
+      <c r="D99" s="27" t="n"/>
+      <c r="E99" s="27" t="n"/>
+      <c r="F99" s="27" t="n"/>
+      <c r="G99" s="27" t="n"/>
+      <c r="H99" s="85" t="n"/>
       <c r="I99" s="15" t="n"/>
       <c r="K99" s="15" t="n"/>
-      <c r="M99" s="85" t="n"/>
+      <c r="M99" s="86" t="n"/>
       <c r="N99" s="15" t="n"/>
-      <c r="O99" s="31" t="n"/>
-    </row>
-    <row r="100" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O99" s="30" t="n"/>
+    </row>
+    <row r="100" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A100" s="15" t="n"/>
-      <c r="B100" s="28" t="n"/>
-      <c r="C100" s="28" t="n"/>
-      <c r="D100" s="28" t="n"/>
-      <c r="E100" s="28" t="n"/>
-      <c r="F100" s="28" t="n"/>
-      <c r="G100" s="28" t="n"/>
-      <c r="H100" s="84" t="n"/>
+      <c r="B100" s="27" t="n"/>
+      <c r="C100" s="27" t="n"/>
+      <c r="D100" s="27" t="n"/>
+      <c r="E100" s="27" t="n"/>
+      <c r="F100" s="27" t="n"/>
+      <c r="G100" s="27" t="n"/>
+      <c r="H100" s="85" t="n"/>
       <c r="I100" s="15" t="n"/>
       <c r="K100" s="15" t="n"/>
-      <c r="M100" s="85" t="n"/>
+      <c r="M100" s="86" t="n"/>
       <c r="N100" s="15" t="n"/>
-      <c r="O100" s="31" t="n"/>
-    </row>
-    <row r="101" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O100" s="30" t="n"/>
+    </row>
+    <row r="101" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A101" s="15" t="n"/>
-      <c r="B101" s="28" t="n"/>
-      <c r="C101" s="28" t="n"/>
-      <c r="D101" s="28" t="n"/>
-      <c r="E101" s="28" t="n"/>
-      <c r="F101" s="28" t="n"/>
-      <c r="G101" s="28" t="n"/>
-      <c r="H101" s="84" t="n"/>
+      <c r="B101" s="27" t="n"/>
+      <c r="C101" s="27" t="n"/>
+      <c r="D101" s="27" t="n"/>
+      <c r="E101" s="27" t="n"/>
+      <c r="F101" s="27" t="n"/>
+      <c r="G101" s="27" t="n"/>
+      <c r="H101" s="85" t="n"/>
       <c r="I101" s="15" t="n"/>
       <c r="K101" s="15" t="n"/>
-      <c r="M101" s="85" t="n"/>
+      <c r="M101" s="86" t="n"/>
       <c r="N101" s="15" t="n"/>
-      <c r="O101" s="31" t="n"/>
-    </row>
-    <row r="102" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O101" s="30" t="n"/>
+    </row>
+    <row r="102" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A102" s="15" t="n"/>
-      <c r="B102" s="28" t="n"/>
-      <c r="C102" s="28" t="n"/>
-      <c r="D102" s="28" t="n"/>
-      <c r="E102" s="28" t="n"/>
-      <c r="F102" s="28" t="n"/>
-      <c r="G102" s="28" t="n"/>
-      <c r="H102" s="84" t="n"/>
+      <c r="B102" s="27" t="n"/>
+      <c r="C102" s="27" t="n"/>
+      <c r="D102" s="27" t="n"/>
+      <c r="E102" s="27" t="n"/>
+      <c r="F102" s="27" t="n"/>
+      <c r="G102" s="27" t="n"/>
+      <c r="H102" s="85" t="n"/>
       <c r="I102" s="15" t="n"/>
       <c r="K102" s="15" t="n"/>
-      <c r="M102" s="85" t="n"/>
+      <c r="M102" s="86" t="n"/>
       <c r="N102" s="15" t="n"/>
-      <c r="O102" s="31" t="n"/>
-    </row>
-    <row r="103" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O102" s="30" t="n"/>
+    </row>
+    <row r="103" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A103" s="15" t="n"/>
-      <c r="B103" s="28" t="n"/>
-      <c r="C103" s="28" t="n"/>
-      <c r="D103" s="28" t="n"/>
-      <c r="E103" s="28" t="n"/>
-      <c r="F103" s="28" t="n"/>
-      <c r="G103" s="28" t="n"/>
-      <c r="H103" s="84" t="n"/>
+      <c r="B103" s="27" t="n"/>
+      <c r="C103" s="27" t="n"/>
+      <c r="D103" s="27" t="n"/>
+      <c r="E103" s="27" t="n"/>
+      <c r="F103" s="27" t="n"/>
+      <c r="G103" s="27" t="n"/>
+      <c r="H103" s="85" t="n"/>
       <c r="I103" s="15" t="n"/>
       <c r="K103" s="15" t="n"/>
-      <c r="M103" s="85" t="n"/>
+      <c r="M103" s="86" t="n"/>
       <c r="N103" s="15" t="n"/>
-      <c r="O103" s="31" t="n"/>
-    </row>
-    <row r="104" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O103" s="30" t="n"/>
+    </row>
+    <row r="104" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A104" s="15" t="n"/>
-      <c r="B104" s="28" t="n"/>
-      <c r="C104" s="28" t="n"/>
-      <c r="D104" s="28" t="n"/>
-      <c r="E104" s="28" t="n"/>
-      <c r="F104" s="28" t="n"/>
-      <c r="G104" s="28" t="n"/>
-      <c r="H104" s="84" t="n"/>
+      <c r="B104" s="27" t="n"/>
+      <c r="C104" s="27" t="n"/>
+      <c r="D104" s="27" t="n"/>
+      <c r="E104" s="27" t="n"/>
+      <c r="F104" s="27" t="n"/>
+      <c r="G104" s="27" t="n"/>
+      <c r="H104" s="85" t="n"/>
       <c r="I104" s="15" t="n"/>
       <c r="K104" s="15" t="n"/>
-      <c r="M104" s="85" t="n"/>
+      <c r="M104" s="86" t="n"/>
       <c r="N104" s="15" t="n"/>
-      <c r="O104" s="31" t="n"/>
-    </row>
-    <row r="105" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O104" s="30" t="n"/>
+    </row>
+    <row r="105" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A105" s="15" t="n"/>
-      <c r="B105" s="28" t="n"/>
-      <c r="C105" s="28" t="n"/>
-      <c r="D105" s="28" t="n"/>
-      <c r="E105" s="28" t="n"/>
-      <c r="F105" s="28" t="n"/>
-      <c r="G105" s="28" t="n"/>
-      <c r="H105" s="84" t="n"/>
+      <c r="B105" s="27" t="n"/>
+      <c r="C105" s="27" t="n"/>
+      <c r="D105" s="27" t="n"/>
+      <c r="E105" s="27" t="n"/>
+      <c r="F105" s="27" t="n"/>
+      <c r="G105" s="27" t="n"/>
+      <c r="H105" s="85" t="n"/>
       <c r="I105" s="15" t="n"/>
       <c r="K105" s="15" t="n"/>
-      <c r="M105" s="85" t="n"/>
+      <c r="M105" s="86" t="n"/>
       <c r="N105" s="15" t="n"/>
-      <c r="O105" s="31" t="n"/>
-    </row>
-    <row r="106" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O105" s="30" t="n"/>
+    </row>
+    <row r="106" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A106" s="15" t="n"/>
-      <c r="B106" s="28" t="n"/>
-      <c r="C106" s="28" t="n"/>
-      <c r="D106" s="28" t="n"/>
-      <c r="E106" s="28" t="n"/>
-      <c r="F106" s="28" t="n"/>
-      <c r="G106" s="28" t="n"/>
-      <c r="H106" s="84" t="n"/>
+      <c r="B106" s="27" t="n"/>
+      <c r="C106" s="27" t="n"/>
+      <c r="D106" s="27" t="n"/>
+      <c r="E106" s="27" t="n"/>
+      <c r="F106" s="27" t="n"/>
+      <c r="G106" s="27" t="n"/>
+      <c r="H106" s="85" t="n"/>
       <c r="I106" s="15" t="n"/>
       <c r="K106" s="15" t="n"/>
-      <c r="M106" s="85" t="n"/>
+      <c r="M106" s="86" t="n"/>
       <c r="N106" s="15" t="n"/>
-      <c r="O106" s="31" t="n"/>
-    </row>
-    <row r="107" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O106" s="30" t="n"/>
+    </row>
+    <row r="107" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A107" s="15" t="n"/>
-      <c r="B107" s="28" t="n"/>
-      <c r="C107" s="28" t="n"/>
-      <c r="D107" s="28" t="n"/>
-      <c r="E107" s="28" t="n"/>
-      <c r="F107" s="28" t="n"/>
-      <c r="G107" s="28" t="n"/>
-      <c r="H107" s="84" t="n"/>
+      <c r="B107" s="27" t="n"/>
+      <c r="C107" s="27" t="n"/>
+      <c r="D107" s="27" t="n"/>
+      <c r="E107" s="27" t="n"/>
+      <c r="F107" s="27" t="n"/>
+      <c r="G107" s="27" t="n"/>
+      <c r="H107" s="85" t="n"/>
       <c r="I107" s="15" t="n"/>
       <c r="K107" s="15" t="n"/>
-      <c r="M107" s="85" t="n"/>
+      <c r="M107" s="86" t="n"/>
       <c r="N107" s="15" t="n"/>
-      <c r="O107" s="31" t="n"/>
-    </row>
-    <row r="108" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O107" s="30" t="n"/>
+    </row>
+    <row r="108" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A108" s="15" t="n"/>
-      <c r="B108" s="28" t="n"/>
-      <c r="C108" s="28" t="n"/>
-      <c r="D108" s="28" t="n"/>
-      <c r="E108" s="28" t="n"/>
-      <c r="F108" s="28" t="n"/>
-      <c r="G108" s="28" t="n"/>
-      <c r="H108" s="84" t="n"/>
+      <c r="B108" s="27" t="n"/>
+      <c r="C108" s="27" t="n"/>
+      <c r="D108" s="27" t="n"/>
+      <c r="E108" s="27" t="n"/>
+      <c r="F108" s="27" t="n"/>
+      <c r="G108" s="27" t="n"/>
+      <c r="H108" s="85" t="n"/>
       <c r="I108" s="15" t="n"/>
       <c r="K108" s="15" t="n"/>
-      <c r="M108" s="85" t="n"/>
+      <c r="M108" s="86" t="n"/>
       <c r="N108" s="15" t="n"/>
-      <c r="O108" s="31" t="n"/>
-    </row>
-    <row r="109" ht="50.1" customFormat="1" customHeight="1" s="82">
+      <c r="O108" s="30" t="n"/>
+    </row>
+    <row r="109" ht="50.1" customFormat="1" customHeight="1" s="78">
       <c r="A109" s="15" t="n"/>
-      <c r="B109" s="28" t="n"/>
-      <c r="C109" s="28" t="n"/>
-      <c r="D109" s="28" t="n"/>
-      <c r="E109" s="28" t="n"/>
-      <c r="F109" s="28" t="n"/>
-      <c r="G109" s="28" t="n"/>
-      <c r="H109" s="84" t="n"/>
+      <c r="B109" s="27" t="n"/>
+      <c r="C109" s="27" t="n"/>
+      <c r="D109" s="27" t="n"/>
+      <c r="E109" s="27" t="n"/>
+      <c r="F109" s="27" t="n"/>
+      <c r="G109" s="27" t="n"/>
+      <c r="H109" s="85" t="n"/>
       <c r="I109" s="15" t="n"/>
       <c r="K109" s="15" t="n"/>
-      <c r="M109" s="85" t="n"/>
+      <c r="M109" s="86" t="n"/>
       <c r="N109" s="15" t="n"/>
-      <c r="O109" s="31" t="n"/>
+      <c r="O109" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3533,11 +3483,11 @@
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="O3:O4"/>
-    <mergeCell ref="H3:H4"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="H3:H4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B5:G49" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
@@ -3566,8 +3516,8 @@
   <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="9" customWidth="1" style="6" min="1" max="1"/>
-    <col width="9" customWidth="1" style="6" min="2" max="16384"/>
+    <col width="9" customWidth="1" style="6" min="1" max="2"/>
+    <col width="9" customWidth="1" style="6" min="3" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3666,7 +3616,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="73" t="inlineStr">
+      <c r="A18" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">　完了した課題は完了日を入れ、行は消さない。（金子主任）　→①に戻る</t>
         </is>
